--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{555A705F-D620-47AA-838B-059DCA53C49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B4FC261-9EE8-423B-8C2C-3C7721E92A68}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{555A705F-D620-47AA-838B-059DCA53C49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD92930E-B7AE-4EB0-85BE-B43B1793FA9E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -535,6 +535,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -4177,7 +4181,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.35">

--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{555A705F-D620-47AA-838B-059DCA53C49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD92930E-B7AE-4EB0-85BE-B43B1793FA9E}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{555A705F-D620-47AA-838B-059DCA53C49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C48510B-17B8-4C64-B559-EE4358F31A04}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="25">
   <si>
     <t>%</t>
   </si>
@@ -341,67 +341,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -857,14 +797,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3833E1-9C55-460E-A922-AEA15E5E66A2}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AS28"/>
+  <dimension ref="A1:AR28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -915,9 +854,8 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
-      <c r="AS1" s="15"/>
-    </row>
-    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
@@ -945,7 +883,7 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
+      <c r="V2" s="18"/>
       <c r="W2" s="18"/>
       <c r="X2" s="18"/>
       <c r="Y2" s="18"/>
@@ -962,15 +900,14 @@
       <c r="AJ2" s="18"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
+      <c r="AM2" s="19"/>
       <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
+      <c r="AO2" s="18"/>
       <c r="AP2" s="18"/>
       <c r="AQ2" s="18"/>
       <c r="AR2" s="18"/>
-      <c r="AS2" s="18"/>
-    </row>
-    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
@@ -998,7 +935,7 @@
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
+      <c r="V3" s="18"/>
       <c r="W3" s="18"/>
       <c r="X3" s="18"/>
       <c r="Y3" s="18"/>
@@ -1015,15 +952,14 @@
       <c r="AJ3" s="18"/>
       <c r="AK3" s="18"/>
       <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
+      <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
+      <c r="AO3" s="18"/>
       <c r="AP3" s="18"/>
       <c r="AQ3" s="18"/>
       <c r="AR3" s="18"/>
-      <c r="AS3" s="18"/>
-    </row>
-    <row r="4" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="1"/>
@@ -1045,7 +981,7 @@
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
+      <c r="V4" s="18"/>
       <c r="W4" s="18"/>
       <c r="X4" s="18"/>
       <c r="Y4" s="18"/>
@@ -1062,15 +998,14 @@
       <c r="AJ4" s="18"/>
       <c r="AK4" s="18"/>
       <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
+      <c r="AM4" s="19"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
+      <c r="AO4" s="18"/>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="18"/>
       <c r="AR4" s="18"/>
-      <c r="AS4" s="18"/>
-    </row>
-    <row r="5" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>16</v>
       </c>
@@ -1098,7 +1033,7 @@
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
+      <c r="V5" s="18"/>
       <c r="W5" s="18"/>
       <c r="X5" s="18"/>
       <c r="Y5" s="18"/>
@@ -1115,15 +1050,14 @@
       <c r="AJ5" s="18"/>
       <c r="AK5" s="18"/>
       <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
+      <c r="AM5" s="19"/>
       <c r="AN5" s="19"/>
-      <c r="AO5" s="19"/>
+      <c r="AO5" s="18"/>
       <c r="AP5" s="18"/>
       <c r="AQ5" s="18"/>
       <c r="AR5" s="18"/>
-      <c r="AS5" s="18"/>
-    </row>
-    <row r="6" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -1143,15 +1077,15 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
+      <c r="V6" s="18"/>
       <c r="W6" s="18"/>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -1168,15 +1102,14 @@
       <c r="AJ6" s="18"/>
       <c r="AK6" s="18"/>
       <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
+      <c r="AM6" s="19"/>
       <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
+      <c r="AO6" s="18"/>
       <c r="AP6" s="18"/>
       <c r="AQ6" s="18"/>
       <c r="AR6" s="18"/>
-      <c r="AS6" s="18"/>
-    </row>
-    <row r="7" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
@@ -1196,15 +1129,15 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="18"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -1221,15 +1154,14 @@
       <c r="AJ7" s="18"/>
       <c r="AK7" s="18"/>
       <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
+      <c r="AM7" s="19"/>
       <c r="AN7" s="19"/>
-      <c r="AO7" s="19"/>
+      <c r="AO7" s="18"/>
       <c r="AP7" s="18"/>
       <c r="AQ7" s="18"/>
       <c r="AR7" s="18"/>
-      <c r="AS7" s="18"/>
-    </row>
-    <row r="8" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
@@ -1257,7 +1189,7 @@
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
+      <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="18"/>
       <c r="Y8" s="18"/>
@@ -1274,15 +1206,14 @@
       <c r="AJ8" s="18"/>
       <c r="AK8" s="18"/>
       <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
+      <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
+      <c r="AO8" s="18"/>
       <c r="AP8" s="18"/>
       <c r="AQ8" s="18"/>
       <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-    </row>
-    <row r="9" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -1304,7 +1235,7 @@
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="18"/>
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
@@ -1321,15 +1252,14 @@
       <c r="AJ9" s="18"/>
       <c r="AK9" s="18"/>
       <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
+      <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
+      <c r="AO9" s="18"/>
       <c r="AP9" s="18"/>
       <c r="AQ9" s="18"/>
       <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-    </row>
-    <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>17</v>
       </c>
@@ -1357,7 +1287,7 @@
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
       <c r="Y10" s="18"/>
@@ -1374,15 +1304,14 @@
       <c r="AJ10" s="18"/>
       <c r="AK10" s="18"/>
       <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
+      <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
+      <c r="AO10" s="18"/>
       <c r="AP10" s="18"/>
       <c r="AQ10" s="18"/>
       <c r="AR10" s="18"/>
-      <c r="AS10" s="18"/>
-    </row>
-    <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
         <v>12</v>
       </c>
@@ -1392,22 +1321,22 @@
       <c r="C11" s="17">
         <v>0</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
@@ -1424,18 +1353,17 @@
       <c r="AG11" s="18"/>
       <c r="AH11" s="18"/>
       <c r="AI11" s="18"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="19"/>
       <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
+      <c r="AL11" s="18"/>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
       <c r="AO11" s="18"/>
       <c r="AP11" s="18"/>
       <c r="AQ11" s="18"/>
       <c r="AR11" s="18"/>
-      <c r="AS11" s="18"/>
-    </row>
-    <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="24" t="s">
         <v>13</v>
       </c>
@@ -1452,15 +1380,15 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -1477,18 +1405,17 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="18"/>
       <c r="AI12" s="18"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="19"/>
       <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
+      <c r="AL12" s="18"/>
       <c r="AM12" s="18"/>
       <c r="AN12" s="18"/>
       <c r="AO12" s="18"/>
       <c r="AP12" s="18"/>
       <c r="AQ12" s="18"/>
       <c r="AR12" s="18"/>
-      <c r="AS12" s="18"/>
-    </row>
-    <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
         <v>1</v>
       </c>
@@ -1513,7 +1440,7 @@
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
@@ -1530,18 +1457,17 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="18"/>
       <c r="AI13" s="18"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="19"/>
       <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
+      <c r="AL13" s="18"/>
       <c r="AM13" s="18"/>
       <c r="AN13" s="18"/>
       <c r="AO13" s="18"/>
       <c r="AP13" s="18"/>
       <c r="AQ13" s="18"/>
       <c r="AR13" s="18"/>
-      <c r="AS13" s="18"/>
-    </row>
-    <row r="14" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -1566,7 +1492,7 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -1583,18 +1509,17 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="19"/>
       <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
+      <c r="AL14" s="18"/>
       <c r="AM14" s="18"/>
       <c r="AN14" s="18"/>
       <c r="AO14" s="18"/>
       <c r="AP14" s="18"/>
       <c r="AQ14" s="18"/>
       <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-    </row>
-    <row r="15" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -1619,7 +1544,7 @@
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -1636,18 +1561,17 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="18"/>
       <c r="AI15" s="18"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="19"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="19"/>
       <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
+      <c r="AO15" s="18"/>
       <c r="AP15" s="18"/>
       <c r="AQ15" s="18"/>
       <c r="AR15" s="18"/>
-      <c r="AS15" s="18"/>
-    </row>
-    <row r="16" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1596,7 @@
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
@@ -1692,15 +1616,14 @@
       <c r="AJ16" s="18"/>
       <c r="AK16" s="18"/>
       <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
+      <c r="AM16" s="19"/>
       <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
+      <c r="AO16" s="18"/>
       <c r="AP16" s="18"/>
       <c r="AQ16" s="18"/>
       <c r="AR16" s="18"/>
-      <c r="AS16" s="18"/>
-    </row>
-    <row r="17" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
       <c r="B17" s="1"/>
       <c r="C17" s="9"/>
@@ -1719,7 +1642,7 @@
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
@@ -1739,15 +1662,14 @@
       <c r="AJ17" s="18"/>
       <c r="AK17" s="18"/>
       <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
+      <c r="AM17" s="19"/>
       <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
+      <c r="AO17" s="18"/>
       <c r="AP17" s="18"/>
       <c r="AQ17" s="18"/>
       <c r="AR17" s="18"/>
-      <c r="AS17" s="18"/>
-    </row>
-    <row r="18" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>19</v>
       </c>
@@ -1758,131 +1680,128 @@
         <v>6</v>
       </c>
       <c r="D18" s="23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="23">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F18" s="23">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G18" s="23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H18" s="23">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I18" s="23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J18" s="23">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K18" s="23">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L18" s="23">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M18" s="23">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N18" s="23">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O18" s="23">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P18" s="23">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q18" s="23">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R18" s="23">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S18" s="23">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T18" s="23">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U18" s="23">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V18" s="23">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W18" s="23">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X18" s="23">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y18" s="23">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z18" s="23">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA18" s="23">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB18" s="23">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC18" s="23">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD18" s="23">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE18" s="23">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF18" s="23">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG18" s="23">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH18" s="23">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI18" s="23">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ18" s="23">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK18" s="23">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL18" s="23">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM18" s="23">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN18" s="23">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO18" s="23">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP18" s="23">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ18" s="23">
-        <v>2059</v>
-      </c>
-      <c r="AR18" s="23">
         <v>2060</v>
       </c>
-      <c r="AS18" s="18"/>
-    </row>
-    <row r="19" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR18" s="18"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
@@ -2012,12 +1931,9 @@
       <c r="AQ19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="AR19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="AS19" s="18"/>
-    </row>
-    <row r="20" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR19" s="18"/>
+    </row>
+    <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
@@ -2147,12 +2063,9 @@
       <c r="AQ20" s="20">
         <v>0</v>
       </c>
-      <c r="AR20" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="18"/>
-    </row>
-    <row r="21" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR20" s="18"/>
+    </row>
+    <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
@@ -2282,12 +2195,9 @@
       <c r="AQ21" s="20">
         <v>0</v>
       </c>
-      <c r="AR21" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS21" s="18"/>
-    </row>
-    <row r="22" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR21" s="18"/>
+    </row>
+    <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2323,18 +2233,17 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="18"/>
       <c r="AI22" s="18"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="19"/>
       <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="19"/>
       <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
+      <c r="AO22" s="18"/>
       <c r="AP22" s="18"/>
       <c r="AQ22" s="18"/>
       <c r="AR22" s="18"/>
-      <c r="AS22" s="18"/>
-    </row>
-    <row r="23" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2370,18 +2279,17 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="18"/>
       <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="19"/>
       <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="18"/>
+      <c r="AL23" s="18"/>
+      <c r="AM23" s="19"/>
       <c r="AN23" s="19"/>
-      <c r="AO23" s="19"/>
+      <c r="AO23" s="18"/>
       <c r="AP23" s="18"/>
       <c r="AQ23" s="18"/>
       <c r="AR23" s="18"/>
-      <c r="AS23" s="18"/>
-    </row>
-    <row r="24" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2417,18 +2325,17 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="18"/>
       <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="19"/>
       <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
+      <c r="AL24" s="18"/>
       <c r="AM24" s="18"/>
       <c r="AN24" s="18"/>
       <c r="AO24" s="18"/>
       <c r="AP24" s="18"/>
       <c r="AQ24" s="18"/>
       <c r="AR24" s="18"/>
-      <c r="AS24" s="18"/>
-    </row>
-    <row r="25" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -2464,51 +2371,42 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="18"/>
       <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="19"/>
       <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
+      <c r="AL25" s="18"/>
       <c r="AM25" s="18"/>
       <c r="AN25" s="18"/>
       <c r="AO25" s="18"/>
       <c r="AP25" s="18"/>
       <c r="AQ25" s="18"/>
       <c r="AR25" s="18"/>
-      <c r="AS25" s="18"/>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A19:AR19">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+  <conditionalFormatting sqref="A19:AQ19 D14:AJ14">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14:AK14">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2519,14 +2417,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AS27"/>
+  <dimension ref="A1:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -2577,9 +2475,8 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
-      <c r="AS1" s="15"/>
-    </row>
-    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
@@ -2607,7 +2504,7 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
+      <c r="V2" s="18"/>
       <c r="W2" s="18"/>
       <c r="X2" s="18"/>
       <c r="Y2" s="18"/>
@@ -2624,15 +2521,14 @@
       <c r="AJ2" s="18"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
+      <c r="AM2" s="19"/>
       <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
+      <c r="AO2" s="18"/>
       <c r="AP2" s="18"/>
       <c r="AQ2" s="18"/>
       <c r="AR2" s="18"/>
-      <c r="AS2" s="18"/>
-    </row>
-    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
@@ -2660,7 +2556,7 @@
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
+      <c r="V3" s="18"/>
       <c r="W3" s="18"/>
       <c r="X3" s="18"/>
       <c r="Y3" s="18"/>
@@ -2677,15 +2573,14 @@
       <c r="AJ3" s="18"/>
       <c r="AK3" s="18"/>
       <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
+      <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
+      <c r="AO3" s="18"/>
       <c r="AP3" s="18"/>
       <c r="AQ3" s="18"/>
       <c r="AR3" s="18"/>
-      <c r="AS3" s="18"/>
-    </row>
-    <row r="4" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="1"/>
@@ -2707,7 +2602,7 @@
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
+      <c r="V4" s="18"/>
       <c r="W4" s="18"/>
       <c r="X4" s="18"/>
       <c r="Y4" s="18"/>
@@ -2724,15 +2619,14 @@
       <c r="AJ4" s="18"/>
       <c r="AK4" s="18"/>
       <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
+      <c r="AM4" s="19"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
+      <c r="AO4" s="18"/>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="18"/>
       <c r="AR4" s="18"/>
-      <c r="AS4" s="18"/>
-    </row>
-    <row r="5" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>16</v>
       </c>
@@ -2760,7 +2654,7 @@
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
+      <c r="V5" s="18"/>
       <c r="W5" s="18"/>
       <c r="X5" s="18"/>
       <c r="Y5" s="18"/>
@@ -2777,15 +2671,14 @@
       <c r="AJ5" s="18"/>
       <c r="AK5" s="18"/>
       <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
+      <c r="AM5" s="19"/>
       <c r="AN5" s="19"/>
-      <c r="AO5" s="19"/>
+      <c r="AO5" s="18"/>
       <c r="AP5" s="18"/>
       <c r="AQ5" s="18"/>
       <c r="AR5" s="18"/>
-      <c r="AS5" s="18"/>
-    </row>
-    <row r="6" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -2805,15 +2698,15 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
+      <c r="V6" s="18"/>
       <c r="W6" s="18"/>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -2830,15 +2723,14 @@
       <c r="AJ6" s="18"/>
       <c r="AK6" s="18"/>
       <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
+      <c r="AM6" s="19"/>
       <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
+      <c r="AO6" s="18"/>
       <c r="AP6" s="18"/>
       <c r="AQ6" s="18"/>
       <c r="AR6" s="18"/>
-      <c r="AS6" s="18"/>
-    </row>
-    <row r="7" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
@@ -2858,15 +2750,15 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="18"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -2883,15 +2775,14 @@
       <c r="AJ7" s="18"/>
       <c r="AK7" s="18"/>
       <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
+      <c r="AM7" s="19"/>
       <c r="AN7" s="19"/>
-      <c r="AO7" s="19"/>
+      <c r="AO7" s="18"/>
       <c r="AP7" s="18"/>
       <c r="AQ7" s="18"/>
       <c r="AR7" s="18"/>
-      <c r="AS7" s="18"/>
-    </row>
-    <row r="8" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
@@ -2919,7 +2810,7 @@
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
+      <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="18"/>
       <c r="Y8" s="18"/>
@@ -2936,15 +2827,14 @@
       <c r="AJ8" s="18"/>
       <c r="AK8" s="18"/>
       <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
+      <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
+      <c r="AO8" s="18"/>
       <c r="AP8" s="18"/>
       <c r="AQ8" s="18"/>
       <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-    </row>
-    <row r="9" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2966,7 +2856,7 @@
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="18"/>
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
@@ -2983,15 +2873,14 @@
       <c r="AJ9" s="18"/>
       <c r="AK9" s="18"/>
       <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
+      <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
+      <c r="AO9" s="18"/>
       <c r="AP9" s="18"/>
       <c r="AQ9" s="18"/>
       <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-    </row>
-    <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>17</v>
       </c>
@@ -3019,7 +2908,7 @@
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
       <c r="Y10" s="18"/>
@@ -3036,15 +2925,14 @@
       <c r="AJ10" s="18"/>
       <c r="AK10" s="18"/>
       <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
+      <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
+      <c r="AO10" s="18"/>
       <c r="AP10" s="18"/>
       <c r="AQ10" s="18"/>
       <c r="AR10" s="18"/>
-      <c r="AS10" s="18"/>
-    </row>
-    <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
         <v>12</v>
       </c>
@@ -3054,22 +2942,22 @@
       <c r="C11" s="17">
         <v>0</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
@@ -3086,18 +2974,17 @@
       <c r="AG11" s="18"/>
       <c r="AH11" s="18"/>
       <c r="AI11" s="18"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="19"/>
       <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
+      <c r="AL11" s="18"/>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
       <c r="AO11" s="18"/>
       <c r="AP11" s="18"/>
       <c r="AQ11" s="18"/>
       <c r="AR11" s="18"/>
-      <c r="AS11" s="18"/>
-    </row>
-    <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="24" t="s">
         <v>13</v>
       </c>
@@ -3114,15 +3001,15 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -3139,18 +3026,17 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="18"/>
       <c r="AI12" s="18"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="19"/>
       <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
+      <c r="AL12" s="18"/>
       <c r="AM12" s="18"/>
       <c r="AN12" s="18"/>
       <c r="AO12" s="18"/>
       <c r="AP12" s="18"/>
       <c r="AQ12" s="18"/>
       <c r="AR12" s="18"/>
-      <c r="AS12" s="18"/>
-    </row>
-    <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
         <v>1</v>
       </c>
@@ -3175,7 +3061,7 @@
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
@@ -3192,18 +3078,17 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="18"/>
       <c r="AI13" s="18"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="19"/>
       <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
+      <c r="AL13" s="18"/>
       <c r="AM13" s="18"/>
       <c r="AN13" s="18"/>
       <c r="AO13" s="18"/>
       <c r="AP13" s="18"/>
       <c r="AQ13" s="18"/>
       <c r="AR13" s="18"/>
-      <c r="AS13" s="18"/>
-    </row>
-    <row r="14" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -3228,7 +3113,7 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -3245,18 +3130,17 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="19"/>
       <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
+      <c r="AL14" s="18"/>
       <c r="AM14" s="18"/>
       <c r="AN14" s="18"/>
       <c r="AO14" s="18"/>
       <c r="AP14" s="18"/>
       <c r="AQ14" s="18"/>
       <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-    </row>
-    <row r="15" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -3281,7 +3165,7 @@
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -3298,18 +3182,17 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="18"/>
       <c r="AI15" s="18"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="19"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="19"/>
       <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
+      <c r="AO15" s="18"/>
       <c r="AP15" s="18"/>
       <c r="AQ15" s="18"/>
       <c r="AR15" s="18"/>
-      <c r="AS15" s="18"/>
-    </row>
-    <row r="16" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>5</v>
       </c>
@@ -3334,7 +3217,7 @@
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
@@ -3354,15 +3237,14 @@
       <c r="AJ16" s="18"/>
       <c r="AK16" s="18"/>
       <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
+      <c r="AM16" s="19"/>
       <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
+      <c r="AO16" s="18"/>
       <c r="AP16" s="18"/>
       <c r="AQ16" s="18"/>
       <c r="AR16" s="18"/>
-      <c r="AS16" s="18"/>
-    </row>
-    <row r="17" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
       <c r="B17" s="1"/>
       <c r="C17" s="9"/>
@@ -3381,7 +3263,7 @@
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
@@ -3401,15 +3283,14 @@
       <c r="AJ17" s="18"/>
       <c r="AK17" s="18"/>
       <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
+      <c r="AM17" s="19"/>
       <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
+      <c r="AO17" s="18"/>
       <c r="AP17" s="18"/>
       <c r="AQ17" s="18"/>
       <c r="AR17" s="18"/>
-      <c r="AS17" s="18"/>
-    </row>
-    <row r="18" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>19</v>
       </c>
@@ -3420,131 +3301,128 @@
         <v>6</v>
       </c>
       <c r="D18" s="23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="23">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F18" s="23">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G18" s="23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H18" s="23">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I18" s="23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J18" s="23">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K18" s="23">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L18" s="23">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M18" s="23">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N18" s="23">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O18" s="23">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P18" s="23">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q18" s="23">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R18" s="23">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S18" s="23">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T18" s="23">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U18" s="23">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V18" s="23">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W18" s="23">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X18" s="23">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y18" s="23">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z18" s="23">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA18" s="23">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB18" s="23">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC18" s="23">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD18" s="23">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE18" s="23">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF18" s="23">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG18" s="23">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH18" s="23">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI18" s="23">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ18" s="23">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK18" s="23">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL18" s="23">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM18" s="23">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN18" s="23">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO18" s="23">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP18" s="23">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ18" s="23">
-        <v>2059</v>
-      </c>
-      <c r="AR18" s="23">
         <v>2060</v>
       </c>
-      <c r="AS18" s="18"/>
-    </row>
-    <row r="19" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR18" s="18"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
@@ -3674,12 +3552,9 @@
       <c r="AQ19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="AR19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="AS19" s="18"/>
-    </row>
-    <row r="20" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR19" s="18"/>
+    </row>
+    <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
@@ -3809,12 +3684,9 @@
       <c r="AQ20" s="20">
         <v>0</v>
       </c>
-      <c r="AR20" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="18"/>
-    </row>
-    <row r="21" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR20" s="18"/>
+    </row>
+    <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
@@ -3944,12 +3816,9 @@
       <c r="AQ21" s="20">
         <v>0</v>
       </c>
-      <c r="AR21" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS21" s="18"/>
-    </row>
-    <row r="22" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR21" s="18"/>
+    </row>
+    <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -3985,18 +3854,17 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="18"/>
       <c r="AI22" s="18"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="19"/>
       <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="19"/>
       <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
+      <c r="AO22" s="18"/>
       <c r="AP22" s="18"/>
       <c r="AQ22" s="18"/>
       <c r="AR22" s="18"/>
-      <c r="AS22" s="18"/>
-    </row>
-    <row r="23" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -4032,18 +3900,17 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="18"/>
       <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="19"/>
       <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="18"/>
+      <c r="AL23" s="18"/>
+      <c r="AM23" s="19"/>
       <c r="AN23" s="19"/>
-      <c r="AO23" s="19"/>
+      <c r="AO23" s="18"/>
       <c r="AP23" s="18"/>
       <c r="AQ23" s="18"/>
       <c r="AR23" s="18"/>
-      <c r="AS23" s="18"/>
-    </row>
-    <row r="24" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -4079,18 +3946,17 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="18"/>
       <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="19"/>
       <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
+      <c r="AL24" s="18"/>
       <c r="AM24" s="18"/>
       <c r="AN24" s="18"/>
       <c r="AO24" s="18"/>
       <c r="AP24" s="18"/>
       <c r="AQ24" s="18"/>
       <c r="AR24" s="18"/>
-      <c r="AS24" s="18"/>
-    </row>
-    <row r="25" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -4126,47 +3992,38 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="18"/>
       <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="19"/>
       <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
+      <c r="AL25" s="18"/>
       <c r="AM25" s="18"/>
       <c r="AN25" s="18"/>
       <c r="AO25" s="18"/>
       <c r="AP25" s="18"/>
       <c r="AQ25" s="18"/>
       <c r="AR25" s="18"/>
-      <c r="AS25" s="18"/>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A19:AR19">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="A19:AQ19 D14:AJ14">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14:AK14">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4177,14 +4034,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1923DA0E-602E-4263-A988-9246800451B4}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AS27"/>
+  <dimension ref="A1:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" customWidth="1"/>
     <col min="3" max="3" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -4235,9 +4092,8 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
-      <c r="AS1" s="15"/>
-    </row>
-    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
@@ -4265,7 +4121,7 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
+      <c r="V2" s="18"/>
       <c r="W2" s="18"/>
       <c r="X2" s="18"/>
       <c r="Y2" s="18"/>
@@ -4282,15 +4138,14 @@
       <c r="AJ2" s="18"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
+      <c r="AM2" s="19"/>
       <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
+      <c r="AO2" s="18"/>
       <c r="AP2" s="18"/>
       <c r="AQ2" s="18"/>
       <c r="AR2" s="18"/>
-      <c r="AS2" s="18"/>
-    </row>
-    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
@@ -4318,7 +4173,7 @@
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
+      <c r="V3" s="18"/>
       <c r="W3" s="18"/>
       <c r="X3" s="18"/>
       <c r="Y3" s="18"/>
@@ -4335,15 +4190,14 @@
       <c r="AJ3" s="18"/>
       <c r="AK3" s="18"/>
       <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
+      <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
+      <c r="AO3" s="18"/>
       <c r="AP3" s="18"/>
       <c r="AQ3" s="18"/>
       <c r="AR3" s="18"/>
-      <c r="AS3" s="18"/>
-    </row>
-    <row r="4" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="1"/>
@@ -4365,7 +4219,7 @@
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
+      <c r="V4" s="18"/>
       <c r="W4" s="18"/>
       <c r="X4" s="18"/>
       <c r="Y4" s="18"/>
@@ -4382,15 +4236,14 @@
       <c r="AJ4" s="18"/>
       <c r="AK4" s="18"/>
       <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
+      <c r="AM4" s="19"/>
       <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
+      <c r="AO4" s="18"/>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="18"/>
       <c r="AR4" s="18"/>
-      <c r="AS4" s="18"/>
-    </row>
-    <row r="5" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>16</v>
       </c>
@@ -4418,7 +4271,7 @@
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
+      <c r="V5" s="18"/>
       <c r="W5" s="18"/>
       <c r="X5" s="18"/>
       <c r="Y5" s="18"/>
@@ -4435,15 +4288,14 @@
       <c r="AJ5" s="18"/>
       <c r="AK5" s="18"/>
       <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
+      <c r="AM5" s="19"/>
       <c r="AN5" s="19"/>
-      <c r="AO5" s="19"/>
+      <c r="AO5" s="18"/>
       <c r="AP5" s="18"/>
       <c r="AQ5" s="18"/>
       <c r="AR5" s="18"/>
-      <c r="AS5" s="18"/>
-    </row>
-    <row r="6" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -4463,15 +4315,15 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
+      <c r="V6" s="18"/>
       <c r="W6" s="18"/>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -4488,15 +4340,14 @@
       <c r="AJ6" s="18"/>
       <c r="AK6" s="18"/>
       <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
+      <c r="AM6" s="19"/>
       <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
+      <c r="AO6" s="18"/>
       <c r="AP6" s="18"/>
       <c r="AQ6" s="18"/>
       <c r="AR6" s="18"/>
-      <c r="AS6" s="18"/>
-    </row>
-    <row r="7" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
@@ -4516,15 +4367,15 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
+      <c r="V7" s="18"/>
       <c r="W7" s="18"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -4541,15 +4392,14 @@
       <c r="AJ7" s="18"/>
       <c r="AK7" s="18"/>
       <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
+      <c r="AM7" s="19"/>
       <c r="AN7" s="19"/>
-      <c r="AO7" s="19"/>
+      <c r="AO7" s="18"/>
       <c r="AP7" s="18"/>
       <c r="AQ7" s="18"/>
       <c r="AR7" s="18"/>
-      <c r="AS7" s="18"/>
-    </row>
-    <row r="8" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
@@ -4577,7 +4427,7 @@
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
+      <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="18"/>
       <c r="Y8" s="18"/>
@@ -4594,15 +4444,14 @@
       <c r="AJ8" s="18"/>
       <c r="AK8" s="18"/>
       <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
+      <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
+      <c r="AO8" s="18"/>
       <c r="AP8" s="18"/>
       <c r="AQ8" s="18"/>
       <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-    </row>
-    <row r="9" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -4624,7 +4473,7 @@
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
+      <c r="V9" s="18"/>
       <c r="W9" s="18"/>
       <c r="X9" s="18"/>
       <c r="Y9" s="18"/>
@@ -4641,15 +4490,14 @@
       <c r="AJ9" s="18"/>
       <c r="AK9" s="18"/>
       <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
+      <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
+      <c r="AO9" s="18"/>
       <c r="AP9" s="18"/>
       <c r="AQ9" s="18"/>
       <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-    </row>
-    <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>17</v>
       </c>
@@ -4677,7 +4525,7 @@
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
+      <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
       <c r="Y10" s="18"/>
@@ -4694,15 +4542,14 @@
       <c r="AJ10" s="18"/>
       <c r="AK10" s="18"/>
       <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
+      <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
+      <c r="AO10" s="18"/>
       <c r="AP10" s="18"/>
       <c r="AQ10" s="18"/>
       <c r="AR10" s="18"/>
-      <c r="AS10" s="18"/>
-    </row>
-    <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
         <v>12</v>
       </c>
@@ -4712,22 +4559,22 @@
       <c r="C11" s="17">
         <v>0</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
@@ -4744,18 +4591,17 @@
       <c r="AG11" s="18"/>
       <c r="AH11" s="18"/>
       <c r="AI11" s="18"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="19"/>
       <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
+      <c r="AL11" s="18"/>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
       <c r="AO11" s="18"/>
       <c r="AP11" s="18"/>
       <c r="AQ11" s="18"/>
       <c r="AR11" s="18"/>
-      <c r="AS11" s="18"/>
-    </row>
-    <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="24" t="s">
         <v>13</v>
       </c>
@@ -4772,15 +4618,15 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -4797,18 +4643,17 @@
       <c r="AG12" s="18"/>
       <c r="AH12" s="18"/>
       <c r="AI12" s="18"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="19"/>
       <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
+      <c r="AL12" s="18"/>
       <c r="AM12" s="18"/>
       <c r="AN12" s="18"/>
       <c r="AO12" s="18"/>
       <c r="AP12" s="18"/>
       <c r="AQ12" s="18"/>
       <c r="AR12" s="18"/>
-      <c r="AS12" s="18"/>
-    </row>
-    <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
         <v>1</v>
       </c>
@@ -4833,7 +4678,7 @@
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
@@ -4850,18 +4695,17 @@
       <c r="AG13" s="18"/>
       <c r="AH13" s="18"/>
       <c r="AI13" s="18"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="19"/>
       <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
+      <c r="AL13" s="18"/>
       <c r="AM13" s="18"/>
       <c r="AN13" s="18"/>
       <c r="AO13" s="18"/>
       <c r="AP13" s="18"/>
       <c r="AQ13" s="18"/>
       <c r="AR13" s="18"/>
-      <c r="AS13" s="18"/>
-    </row>
-    <row r="14" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -4886,7 +4730,7 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -4903,18 +4747,17 @@
       <c r="AG14" s="18"/>
       <c r="AH14" s="18"/>
       <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
+      <c r="AJ14" s="19"/>
       <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
+      <c r="AL14" s="18"/>
       <c r="AM14" s="18"/>
       <c r="AN14" s="18"/>
       <c r="AO14" s="18"/>
       <c r="AP14" s="18"/>
       <c r="AQ14" s="18"/>
       <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-    </row>
-    <row r="15" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -4939,7 +4782,7 @@
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -4956,18 +4799,17 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="18"/>
       <c r="AI15" s="18"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="19"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="19"/>
       <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
+      <c r="AO15" s="18"/>
       <c r="AP15" s="18"/>
       <c r="AQ15" s="18"/>
       <c r="AR15" s="18"/>
-      <c r="AS15" s="18"/>
-    </row>
-    <row r="16" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>5</v>
       </c>
@@ -4992,7 +4834,7 @@
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
@@ -5012,15 +4854,14 @@
       <c r="AJ16" s="18"/>
       <c r="AK16" s="18"/>
       <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
+      <c r="AM16" s="19"/>
       <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
+      <c r="AO16" s="18"/>
       <c r="AP16" s="18"/>
       <c r="AQ16" s="18"/>
       <c r="AR16" s="18"/>
-      <c r="AS16" s="18"/>
-    </row>
-    <row r="17" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
       <c r="B17" s="1"/>
       <c r="C17" s="9"/>
@@ -5039,7 +4880,7 @@
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
@@ -5059,15 +4900,14 @@
       <c r="AJ17" s="18"/>
       <c r="AK17" s="18"/>
       <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
+      <c r="AM17" s="19"/>
       <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
+      <c r="AO17" s="18"/>
       <c r="AP17" s="18"/>
       <c r="AQ17" s="18"/>
       <c r="AR17" s="18"/>
-      <c r="AS17" s="18"/>
-    </row>
-    <row r="18" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>19</v>
       </c>
@@ -5078,131 +4918,128 @@
         <v>6</v>
       </c>
       <c r="D18" s="23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="23">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F18" s="23">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G18" s="23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H18" s="23">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I18" s="23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J18" s="23">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K18" s="23">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L18" s="23">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M18" s="23">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N18" s="23">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O18" s="23">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P18" s="23">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q18" s="23">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R18" s="23">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S18" s="23">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T18" s="23">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U18" s="23">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V18" s="23">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W18" s="23">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X18" s="23">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y18" s="23">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z18" s="23">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA18" s="23">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB18" s="23">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC18" s="23">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD18" s="23">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE18" s="23">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF18" s="23">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG18" s="23">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH18" s="23">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI18" s="23">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ18" s="23">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK18" s="23">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL18" s="23">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM18" s="23">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN18" s="23">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO18" s="23">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP18" s="23">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ18" s="23">
-        <v>2059</v>
-      </c>
-      <c r="AR18" s="23">
         <v>2060</v>
       </c>
-      <c r="AS18" s="18"/>
-    </row>
-    <row r="19" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR18" s="18"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
@@ -5332,12 +5169,9 @@
       <c r="AQ19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="AR19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="AS19" s="18"/>
-    </row>
-    <row r="20" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR19" s="18"/>
+    </row>
+    <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
@@ -5467,12 +5301,9 @@
       <c r="AQ20" s="20">
         <v>0</v>
       </c>
-      <c r="AR20" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="18"/>
-    </row>
-    <row r="21" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR20" s="18"/>
+    </row>
+    <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
@@ -5602,12 +5433,9 @@
       <c r="AQ21" s="20">
         <v>0</v>
       </c>
-      <c r="AR21" s="20">
-        <v>0</v>
-      </c>
-      <c r="AS21" s="18"/>
-    </row>
-    <row r="22" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AR21" s="18"/>
+    </row>
+    <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -5643,18 +5471,17 @@
       <c r="AG22" s="18"/>
       <c r="AH22" s="18"/>
       <c r="AI22" s="18"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="19"/>
       <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="19"/>
       <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
+      <c r="AO22" s="18"/>
       <c r="AP22" s="18"/>
       <c r="AQ22" s="18"/>
       <c r="AR22" s="18"/>
-      <c r="AS22" s="18"/>
-    </row>
-    <row r="23" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -5690,18 +5517,17 @@
       <c r="AG23" s="18"/>
       <c r="AH23" s="18"/>
       <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="19"/>
       <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="18"/>
+      <c r="AL23" s="18"/>
+      <c r="AM23" s="19"/>
       <c r="AN23" s="19"/>
-      <c r="AO23" s="19"/>
+      <c r="AO23" s="18"/>
       <c r="AP23" s="18"/>
       <c r="AQ23" s="18"/>
       <c r="AR23" s="18"/>
-      <c r="AS23" s="18"/>
-    </row>
-    <row r="24" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -5737,18 +5563,17 @@
       <c r="AG24" s="18"/>
       <c r="AH24" s="18"/>
       <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
+      <c r="AJ24" s="19"/>
       <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
+      <c r="AL24" s="18"/>
       <c r="AM24" s="18"/>
       <c r="AN24" s="18"/>
       <c r="AO24" s="18"/>
       <c r="AP24" s="18"/>
       <c r="AQ24" s="18"/>
       <c r="AR24" s="18"/>
-      <c r="AS24" s="18"/>
-    </row>
-    <row r="25" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -5784,47 +5609,38 @@
       <c r="AG25" s="18"/>
       <c r="AH25" s="18"/>
       <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="19"/>
       <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
+      <c r="AL25" s="18"/>
       <c r="AM25" s="18"/>
       <c r="AN25" s="18"/>
       <c r="AO25" s="18"/>
       <c r="AP25" s="18"/>
       <c r="AQ25" s="18"/>
       <c r="AR25" s="18"/>
-      <c r="AS25" s="18"/>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A19:AR19">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+  <conditionalFormatting sqref="A19:AQ19 D14:AJ14">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14:AK14">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1216790-B00B-4E2C-A816-3B18E3C82F68}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="53">
   <si>
     <t>%</t>
   </si>
@@ -97,9 +97,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>GRID</t>
-  </si>
-  <si>
     <t>Total - GRID</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>Amortization period - GRID</t>
-  </si>
-  <si>
-    <t>OFF-GRID</t>
   </si>
   <si>
     <t>Total - OFF-GRID</t>
@@ -184,9 +178,6 @@
     <t>Cost of Debt - GRID</t>
   </si>
   <si>
-    <t>WACC- GRID</t>
-  </si>
-  <si>
     <t>Cost of Equity - OFF-GRID</t>
   </si>
   <si>
@@ -200,6 +191,12 @@
   </si>
   <si>
     <t>Amortization period -OFF-GRID</t>
+  </si>
+  <si>
+    <t>WACC - GRID</t>
+  </si>
+  <si>
+    <t>How much to be financed</t>
   </si>
 </sst>
 </file>
@@ -355,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -423,344 +420,15 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="56">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1337,7 +1005,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3833E1-9C55-460E-A922-AEA15E5E66A2}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AR46"/>
+  <dimension ref="A1:AR44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.54296875" customWidth="1"/>
@@ -1397,7 +1065,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>7</v>
@@ -1497,8 +1165,12 @@
       <c r="A4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>9</v>
+      </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
@@ -1542,14 +1214,14 @@
       <c r="AR4" s="18"/>
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>9</v>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -1561,7 +1233,7 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
+      <c r="N5" s="2"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -1595,7 +1267,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -1647,7 +1319,7 @@
     </row>
     <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -1665,7 +1337,7 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -1698,15 +1370,9 @@
       <c r="AR7" s="18"/>
     </row>
     <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="20">
-        <v>0</v>
-      </c>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -1750,9 +1416,15 @@
       <c r="AR8" s="18"/>
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="A9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>9</v>
+      </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -1796,14 +1468,14 @@
       <c r="AR9" s="18"/>
     </row>
     <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>9</v>
+      <c r="B10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1812,7 +1484,7 @@
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="K10" s="2"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
@@ -1820,9 +1492,9 @@
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
       <c r="V10" s="18"/>
       <c r="W10" s="18"/>
       <c r="X10" s="18"/>
@@ -1837,24 +1509,24 @@
       <c r="AG10" s="18"/>
       <c r="AH10" s="18"/>
       <c r="AI10" s="18"/>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="18"/>
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="19"/>
       <c r="AL10" s="18"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
+      <c r="AM10" s="18"/>
+      <c r="AN10" s="18"/>
       <c r="AO10" s="18"/>
       <c r="AP10" s="18"/>
       <c r="AQ10" s="18"/>
       <c r="AR10" s="18"/>
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>25</v>
+      <c r="A11" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="20">
         <v>0</v>
       </c>
       <c r="D11" s="9"/>
@@ -1900,13 +1572,13 @@
       <c r="AR11" s="18"/>
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="16" t="s">
-        <v>45</v>
+      <c r="A12" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="17">
         <v>0</v>
       </c>
       <c r="D12" s="9"/>
@@ -1916,7 +1588,7 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
@@ -1953,13 +1625,13 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="17">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>18</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2004,14 +1676,14 @@
       <c r="AR13" s="18"/>
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>18</v>
+      <c r="A14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -2048,8 +1720,8 @@
       <c r="AJ14" s="19"/>
       <c r="AK14" s="19"/>
       <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="18"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="19"/>
       <c r="AO14" s="18"/>
       <c r="AP14" s="18"/>
       <c r="AQ14" s="18"/>
@@ -2057,10 +1729,10 @@
     </row>
     <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="20">
         <v>0</v>
@@ -2097,8 +1769,8 @@
       <c r="AG15" s="18"/>
       <c r="AH15" s="18"/>
       <c r="AI15" s="18"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="18"/>
       <c r="AL15" s="18"/>
       <c r="AM15" s="19"/>
       <c r="AN15" s="19"/>
@@ -2160,13 +1832,13 @@
       <c r="AR16" s="18"/>
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A17" s="16" t="s">
-        <v>28</v>
+      <c r="A17" s="24" t="s">
+        <v>51</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17">
         <v>0</v>
       </c>
       <c r="D17" s="9"/>
@@ -2212,15 +1884,9 @@
       <c r="AR17" s="18"/>
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17">
-        <v>0</v>
-      </c>
+      <c r="A18" s="9"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -2264,9 +1930,15 @@
       <c r="AR18" s="18"/>
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>9</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -2310,11 +1982,15 @@
       <c r="AR19" s="18"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20">
+        <v>0</v>
+      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -2358,14 +2034,14 @@
       <c r="AR20" s="18"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>9</v>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="20">
+        <v>0</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -2462,15 +2138,9 @@
       <c r="AR22" s="18"/>
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="20">
-        <v>0</v>
-      </c>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -2514,14 +2184,14 @@
       <c r="AR23" s="18"/>
     </row>
     <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="20">
-        <v>0</v>
+      <c r="A24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -2566,9 +2236,15 @@
       <c r="AR24" s="18"/>
     </row>
     <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="17">
+        <v>0</v>
+      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -2612,14 +2288,14 @@
       <c r="AR25" s="18"/>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>9</v>
+      <c r="A26" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="20">
+        <v>0</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -2665,7 +2341,7 @@
     </row>
     <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>0</v>
@@ -2716,14 +2392,14 @@
       <c r="AR27" s="18"/>
     </row>
     <row r="28" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A28" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20">
-        <v>0</v>
+      <c r="A28" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>18</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -2768,13 +2444,13 @@
       <c r="AR28" s="18"/>
     </row>
     <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A29" s="24" t="s">
-        <v>36</v>
+      <c r="A29" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="20">
         <v>0</v>
       </c>
       <c r="D29" s="9"/>
@@ -2820,14 +2496,14 @@
       <c r="AR29" s="18"/>
     </row>
     <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A30" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>18</v>
+      <c r="A30" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -2873,10 +2549,10 @@
     </row>
     <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C31" s="20">
         <v>0</v>
@@ -2924,13 +2600,13 @@
       <c r="AR31" s="18"/>
     </row>
     <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A32" s="16" t="s">
-        <v>37</v>
+      <c r="A32" s="24" t="s">
+        <v>49</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="20">
+        <v>0</v>
+      </c>
+      <c r="C32" s="17">
         <v>0</v>
       </c>
       <c r="D32" s="9"/>
@@ -2976,15 +2652,9 @@
       <c r="AR32" s="18"/>
     </row>
     <row r="33" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="20">
-        <v>0</v>
-      </c>
+      <c r="A33" s="8"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -3028,629 +2698,3072 @@
       <c r="AR33" s="18"/>
     </row>
     <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="17">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="18"/>
-      <c r="AD34" s="18"/>
-      <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
-      <c r="AG34" s="18"/>
-      <c r="AH34" s="18"/>
-      <c r="AI34" s="18"/>
-      <c r="AJ34" s="18"/>
-      <c r="AK34" s="18"/>
-      <c r="AL34" s="18"/>
-      <c r="AM34" s="19"/>
-      <c r="AN34" s="19"/>
-      <c r="AO34" s="18"/>
-      <c r="AP34" s="18"/>
-      <c r="AQ34" s="18"/>
+      <c r="A34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="23">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="23">
+        <v>2022</v>
+      </c>
+      <c r="F34" s="23">
+        <v>2023</v>
+      </c>
+      <c r="G34" s="23">
+        <v>2024</v>
+      </c>
+      <c r="H34" s="23">
+        <v>2025</v>
+      </c>
+      <c r="I34" s="23">
+        <v>2026</v>
+      </c>
+      <c r="J34" s="23">
+        <v>2027</v>
+      </c>
+      <c r="K34" s="23">
+        <v>2028</v>
+      </c>
+      <c r="L34" s="23">
+        <v>2029</v>
+      </c>
+      <c r="M34" s="23">
+        <v>2030</v>
+      </c>
+      <c r="N34" s="23">
+        <v>2031</v>
+      </c>
+      <c r="O34" s="23">
+        <v>2032</v>
+      </c>
+      <c r="P34" s="23">
+        <v>2033</v>
+      </c>
+      <c r="Q34" s="23">
+        <v>2034</v>
+      </c>
+      <c r="R34" s="23">
+        <v>2035</v>
+      </c>
+      <c r="S34" s="23">
+        <v>2036</v>
+      </c>
+      <c r="T34" s="23">
+        <v>2037</v>
+      </c>
+      <c r="U34" s="23">
+        <v>2038</v>
+      </c>
+      <c r="V34" s="23">
+        <v>2039</v>
+      </c>
+      <c r="W34" s="23">
+        <v>2040</v>
+      </c>
+      <c r="X34" s="23">
+        <v>2041</v>
+      </c>
+      <c r="Y34" s="23">
+        <v>2042</v>
+      </c>
+      <c r="Z34" s="23">
+        <v>2043</v>
+      </c>
+      <c r="AA34" s="23">
+        <v>2044</v>
+      </c>
+      <c r="AB34" s="23">
+        <v>2045</v>
+      </c>
+      <c r="AC34" s="23">
+        <v>2046</v>
+      </c>
+      <c r="AD34" s="23">
+        <v>2047</v>
+      </c>
+      <c r="AE34" s="23">
+        <v>2048</v>
+      </c>
+      <c r="AF34" s="23">
+        <v>2049</v>
+      </c>
+      <c r="AG34" s="23">
+        <v>2050</v>
+      </c>
+      <c r="AH34" s="23">
+        <v>2051</v>
+      </c>
+      <c r="AI34" s="23">
+        <v>2052</v>
+      </c>
+      <c r="AJ34" s="23">
+        <v>2053</v>
+      </c>
+      <c r="AK34" s="23">
+        <v>2054</v>
+      </c>
+      <c r="AL34" s="23">
+        <v>2055</v>
+      </c>
+      <c r="AM34" s="23">
+        <v>2056</v>
+      </c>
+      <c r="AN34" s="23">
+        <v>2057</v>
+      </c>
+      <c r="AO34" s="23">
+        <v>2058</v>
+      </c>
+      <c r="AP34" s="23">
+        <v>2059</v>
+      </c>
+      <c r="AQ34" s="23">
+        <v>2060</v>
+      </c>
       <c r="AR34" s="18"/>
     </row>
     <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A35" s="8"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="18"/>
-      <c r="AE35" s="18"/>
-      <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="18"/>
-      <c r="AI35" s="18"/>
-      <c r="AJ35" s="18"/>
-      <c r="AK35" s="18"/>
-      <c r="AL35" s="18"/>
-      <c r="AM35" s="19"/>
-      <c r="AN35" s="19"/>
-      <c r="AO35" s="18"/>
-      <c r="AP35" s="18"/>
-      <c r="AQ35" s="18"/>
+      <c r="A35" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="U35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="V35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="W35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="X35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ35" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="AR35" s="18"/>
     </row>
     <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="23">
-        <v>2021</v>
-      </c>
-      <c r="E36" s="23">
-        <v>2022</v>
-      </c>
-      <c r="F36" s="23">
-        <v>2023</v>
-      </c>
-      <c r="G36" s="23">
-        <v>2024</v>
-      </c>
-      <c r="H36" s="23">
-        <v>2025</v>
-      </c>
-      <c r="I36" s="23">
-        <v>2026</v>
-      </c>
-      <c r="J36" s="23">
-        <v>2027</v>
-      </c>
-      <c r="K36" s="23">
-        <v>2028</v>
-      </c>
-      <c r="L36" s="23">
-        <v>2029</v>
-      </c>
-      <c r="M36" s="23">
-        <v>2030</v>
-      </c>
-      <c r="N36" s="23">
-        <v>2031</v>
-      </c>
-      <c r="O36" s="23">
-        <v>2032</v>
-      </c>
-      <c r="P36" s="23">
-        <v>2033</v>
-      </c>
-      <c r="Q36" s="23">
-        <v>2034</v>
-      </c>
-      <c r="R36" s="23">
-        <v>2035</v>
-      </c>
-      <c r="S36" s="23">
-        <v>2036</v>
-      </c>
-      <c r="T36" s="23">
-        <v>2037</v>
-      </c>
-      <c r="U36" s="23">
-        <v>2038</v>
-      </c>
-      <c r="V36" s="23">
-        <v>2039</v>
-      </c>
-      <c r="W36" s="23">
-        <v>2040</v>
-      </c>
-      <c r="X36" s="23">
-        <v>2041</v>
-      </c>
-      <c r="Y36" s="23">
-        <v>2042</v>
-      </c>
-      <c r="Z36" s="23">
-        <v>2043</v>
-      </c>
-      <c r="AA36" s="23">
-        <v>2044</v>
-      </c>
-      <c r="AB36" s="23">
-        <v>2045</v>
-      </c>
-      <c r="AC36" s="23">
-        <v>2046</v>
-      </c>
-      <c r="AD36" s="23">
-        <v>2047</v>
-      </c>
-      <c r="AE36" s="23">
-        <v>2048</v>
-      </c>
-      <c r="AF36" s="23">
-        <v>2049</v>
-      </c>
-      <c r="AG36" s="23">
-        <v>2050</v>
-      </c>
-      <c r="AH36" s="23">
-        <v>2051</v>
-      </c>
-      <c r="AI36" s="23">
-        <v>2052</v>
-      </c>
-      <c r="AJ36" s="23">
-        <v>2053</v>
-      </c>
-      <c r="AK36" s="23">
-        <v>2054</v>
-      </c>
-      <c r="AL36" s="23">
-        <v>2055</v>
-      </c>
-      <c r="AM36" s="23">
-        <v>2056</v>
-      </c>
-      <c r="AN36" s="23">
-        <v>2057</v>
-      </c>
-      <c r="AO36" s="23">
-        <v>2058</v>
-      </c>
-      <c r="AP36" s="23">
-        <v>2059</v>
-      </c>
-      <c r="AQ36" s="23">
-        <v>2060</v>
+      <c r="A36" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="20">
+        <v>0</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0</v>
+      </c>
+      <c r="F36" s="20">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <v>0</v>
+      </c>
+      <c r="H36" s="20">
+        <v>0</v>
+      </c>
+      <c r="I36" s="20">
+        <v>0</v>
+      </c>
+      <c r="J36" s="20">
+        <v>0</v>
+      </c>
+      <c r="K36" s="20">
+        <v>0</v>
+      </c>
+      <c r="L36" s="20">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20">
+        <v>0</v>
+      </c>
+      <c r="P36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="20">
+        <v>0</v>
+      </c>
+      <c r="R36" s="20">
+        <v>0</v>
+      </c>
+      <c r="S36" s="20">
+        <v>0</v>
+      </c>
+      <c r="T36" s="20">
+        <v>0</v>
+      </c>
+      <c r="U36" s="20">
+        <v>0</v>
+      </c>
+      <c r="V36" s="20">
+        <v>0</v>
+      </c>
+      <c r="W36" s="20">
+        <v>0</v>
+      </c>
+      <c r="X36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="20">
+        <v>0</v>
       </c>
       <c r="AR36" s="18"/>
     </row>
     <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>0</v>
+      </c>
+      <c r="P37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="20">
+        <v>0</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
+        <v>0</v>
+      </c>
+      <c r="T37" s="20">
+        <v>0</v>
+      </c>
+      <c r="U37" s="20">
+        <v>0</v>
+      </c>
+      <c r="V37" s="20">
+        <v>0</v>
+      </c>
+      <c r="W37" s="20">
+        <v>0</v>
+      </c>
+      <c r="X37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="18"/>
+    </row>
+    <row r="38" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+      <c r="AG38" s="18"/>
+      <c r="AH38" s="18"/>
+      <c r="AI38" s="18"/>
+      <c r="AJ38" s="19"/>
+      <c r="AK38" s="19"/>
+      <c r="AL38" s="18"/>
+      <c r="AM38" s="19"/>
+      <c r="AN38" s="19"/>
+      <c r="AO38" s="18"/>
+      <c r="AP38" s="18"/>
+      <c r="AQ38" s="18"/>
+      <c r="AR38" s="18"/>
+    </row>
+    <row r="39" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="18"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
+      <c r="AF39" s="18"/>
+      <c r="AG39" s="18"/>
+      <c r="AH39" s="18"/>
+      <c r="AI39" s="18"/>
+      <c r="AJ39" s="19"/>
+      <c r="AK39" s="19"/>
+      <c r="AL39" s="18"/>
+      <c r="AM39" s="19"/>
+      <c r="AN39" s="19"/>
+      <c r="AO39" s="18"/>
+      <c r="AP39" s="18"/>
+      <c r="AQ39" s="18"/>
+      <c r="AR39" s="18"/>
+    </row>
+    <row r="40" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="18"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="18"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="18"/>
+      <c r="AI40" s="18"/>
+      <c r="AJ40" s="19"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="18"/>
+      <c r="AM40" s="18"/>
+      <c r="AN40" s="18"/>
+      <c r="AO40" s="18"/>
+      <c r="AP40" s="18"/>
+      <c r="AQ40" s="18"/>
+      <c r="AR40" s="18"/>
+    </row>
+    <row r="41" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="18"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
+      <c r="AF41" s="18"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="18"/>
+      <c r="AI41" s="18"/>
+      <c r="AJ41" s="19"/>
+      <c r="AK41" s="19"/>
+      <c r="AL41" s="18"/>
+      <c r="AM41" s="18"/>
+      <c r="AN41" s="18"/>
+      <c r="AO41" s="18"/>
+      <c r="AP41" s="18"/>
+      <c r="AQ41" s="18"/>
+      <c r="AR41" s="18"/>
+    </row>
+    <row r="42" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ42" s="3"/>
+      <c r="AK42" s="3"/>
+    </row>
+    <row r="43" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ43" s="3"/>
+      <c r="AK43" s="3"/>
+    </row>
+    <row r="44" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AJ44" s="3"/>
+      <c r="AK44" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A35:AQ35">
+    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:AJ13">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A1:AR42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:44" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+    </row>
+    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="17">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="18"/>
+      <c r="AP2" s="18"/>
+      <c r="AQ2" s="18"/>
+      <c r="AR2" s="18"/>
+    </row>
+    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AA3" s="18"/>
+      <c r="AB3" s="18"/>
+      <c r="AC3" s="18"/>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="18"/>
+    </row>
+    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="18"/>
+      <c r="Y4" s="18"/>
+      <c r="Z4" s="18"/>
+      <c r="AA4" s="18"/>
+      <c r="AB4" s="18"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="18"/>
+      <c r="AF4" s="18"/>
+      <c r="AG4" s="18"/>
+      <c r="AH4" s="18"/>
+      <c r="AI4" s="18"/>
+      <c r="AJ4" s="18"/>
+      <c r="AK4" s="18"/>
+      <c r="AL4" s="18"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="18"/>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="18"/>
+      <c r="AR4" s="18"/>
+    </row>
+    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+      <c r="Z5" s="18"/>
+      <c r="AA5" s="18"/>
+      <c r="AB5" s="18"/>
+      <c r="AC5" s="18"/>
+      <c r="AD5" s="18"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18"/>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
+      <c r="AR5" s="18"/>
+    </row>
+    <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="18"/>
+      <c r="AA6" s="18"/>
+      <c r="AB6" s="18"/>
+      <c r="AC6" s="18"/>
+      <c r="AD6" s="18"/>
+      <c r="AE6" s="18"/>
+      <c r="AF6" s="18"/>
+      <c r="AG6" s="18"/>
+      <c r="AH6" s="18"/>
+      <c r="AI6" s="18"/>
+      <c r="AJ6" s="18"/>
+      <c r="AK6" s="18"/>
+      <c r="AL6" s="18"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="18"/>
+      <c r="AP6" s="18"/>
+      <c r="AQ6" s="18"/>
+      <c r="AR6" s="18"/>
+    </row>
+    <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="18"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="18"/>
+      <c r="Z7" s="18"/>
+      <c r="AA7" s="18"/>
+      <c r="AB7" s="18"/>
+      <c r="AC7" s="18"/>
+      <c r="AD7" s="18"/>
+      <c r="AE7" s="18"/>
+      <c r="AF7" s="18"/>
+      <c r="AG7" s="18"/>
+      <c r="AH7" s="18"/>
+      <c r="AI7" s="18"/>
+      <c r="AJ7" s="18"/>
+      <c r="AK7" s="18"/>
+      <c r="AL7" s="18"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="18"/>
+      <c r="AP7" s="18"/>
+      <c r="AQ7" s="18"/>
+      <c r="AR7" s="18"/>
+    </row>
+    <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="18"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="18"/>
+      <c r="AG8" s="18"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="18"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="18"/>
+      <c r="AQ8" s="18"/>
+      <c r="AR8" s="18"/>
+    </row>
+    <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="18"/>
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="18"/>
+      <c r="AG9" s="18"/>
+      <c r="AH9" s="18"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="18"/>
+      <c r="AP9" s="18"/>
+      <c r="AQ9" s="18"/>
+      <c r="AR9" s="18"/>
+    </row>
+    <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="18"/>
+      <c r="X10" s="18"/>
+      <c r="Y10" s="18"/>
+      <c r="Z10" s="18"/>
+      <c r="AA10" s="18"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="18"/>
+      <c r="AE10" s="18"/>
+      <c r="AF10" s="18"/>
+      <c r="AG10" s="18"/>
+      <c r="AH10" s="18"/>
+      <c r="AI10" s="18"/>
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="19"/>
+      <c r="AL10" s="18"/>
+      <c r="AM10" s="18"/>
+      <c r="AN10" s="18"/>
+      <c r="AO10" s="18"/>
+      <c r="AP10" s="18"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="18"/>
+    </row>
+    <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="18"/>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="18"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="18"/>
+      <c r="AN11" s="18"/>
+      <c r="AO11" s="18"/>
+      <c r="AP11" s="18"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="18"/>
+    </row>
+    <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="18"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="18"/>
+      <c r="AA12" s="18"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="18"/>
+      <c r="AF12" s="18"/>
+      <c r="AG12" s="18"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="18"/>
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="18"/>
+      <c r="AM12" s="18"/>
+      <c r="AN12" s="18"/>
+      <c r="AO12" s="18"/>
+      <c r="AP12" s="18"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="18"/>
+    </row>
+    <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A13" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="18"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="18"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="18"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="18"/>
+      <c r="AO13" s="18"/>
+      <c r="AP13" s="18"/>
+      <c r="AQ13" s="18"/>
+      <c r="AR13" s="18"/>
+    </row>
+    <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="18"/>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="18"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="18"/>
+      <c r="AE14" s="18"/>
+      <c r="AF14" s="18"/>
+      <c r="AG14" s="18"/>
+      <c r="AH14" s="18"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="19"/>
+      <c r="AK14" s="19"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="19"/>
+      <c r="AO14" s="18"/>
+      <c r="AP14" s="18"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="18"/>
+    </row>
+    <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A15" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="18"/>
+      <c r="Z15" s="18"/>
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="18"/>
+      <c r="AG15" s="18"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="18"/>
+      <c r="AP15" s="18"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="18"/>
+    </row>
+    <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="20">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="18"/>
+      <c r="Z16" s="18"/>
+      <c r="AA16" s="18"/>
+      <c r="AB16" s="18"/>
+      <c r="AC16" s="18"/>
+      <c r="AD16" s="18"/>
+      <c r="AE16" s="18"/>
+      <c r="AF16" s="18"/>
+      <c r="AG16" s="18"/>
+      <c r="AH16" s="18"/>
+      <c r="AI16" s="18"/>
+      <c r="AJ16" s="18"/>
+      <c r="AK16" s="18"/>
+      <c r="AL16" s="18"/>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="19"/>
+      <c r="AO16" s="18"/>
+      <c r="AP16" s="18"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="18"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="18"/>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="18"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="18"/>
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="18"/>
+      <c r="AP17" s="18"/>
+      <c r="AQ17" s="18"/>
+      <c r="AR17" s="18"/>
+    </row>
+    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="18"/>
+      <c r="X18" s="18"/>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="18"/>
+      <c r="AE18" s="18"/>
+      <c r="AF18" s="18"/>
+      <c r="AG18" s="18"/>
+      <c r="AH18" s="18"/>
+      <c r="AI18" s="18"/>
+      <c r="AJ18" s="18"/>
+      <c r="AK18" s="18"/>
+      <c r="AL18" s="18"/>
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="19"/>
+      <c r="AO18" s="18"/>
+      <c r="AP18" s="18"/>
+      <c r="AQ18" s="18"/>
+      <c r="AR18" s="18"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="18"/>
+      <c r="AE19" s="18"/>
+      <c r="AF19" s="18"/>
+      <c r="AG19" s="18"/>
+      <c r="AH19" s="18"/>
+      <c r="AI19" s="18"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="18"/>
+      <c r="AL19" s="18"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="19"/>
+      <c r="AO19" s="18"/>
+      <c r="AP19" s="18"/>
+      <c r="AQ19" s="18"/>
+      <c r="AR19" s="18"/>
+    </row>
+    <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="18"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="18"/>
+      <c r="AG20" s="18"/>
+      <c r="AH20" s="18"/>
+      <c r="AI20" s="18"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="18"/>
+      <c r="AL20" s="18"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="19"/>
+      <c r="AO20" s="18"/>
+      <c r="AP20" s="18"/>
+      <c r="AQ20" s="18"/>
+      <c r="AR20" s="18"/>
+    </row>
+    <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="20">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
+      <c r="AF21" s="18"/>
+      <c r="AG21" s="18"/>
+      <c r="AH21" s="18"/>
+      <c r="AI21" s="18"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="18"/>
+      <c r="AL21" s="18"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="18"/>
+      <c r="AP21" s="18"/>
+      <c r="AQ21" s="18"/>
+      <c r="AR21" s="18"/>
+    </row>
+    <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="20">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
+      <c r="AF22" s="18"/>
+      <c r="AG22" s="18"/>
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="18"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="19"/>
+      <c r="AO22" s="18"/>
+      <c r="AP22" s="18"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="18"/>
+    </row>
+    <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="18"/>
+      <c r="AE23" s="18"/>
+      <c r="AF23" s="18"/>
+      <c r="AG23" s="18"/>
+      <c r="AH23" s="18"/>
+      <c r="AI23" s="18"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="18"/>
+      <c r="AL23" s="18"/>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="19"/>
+      <c r="AO23" s="18"/>
+      <c r="AP23" s="18"/>
+      <c r="AQ23" s="18"/>
+      <c r="AR23" s="18"/>
+    </row>
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="18"/>
+      <c r="AL24" s="18"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="19"/>
+      <c r="AO24" s="18"/>
+      <c r="AP24" s="18"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="18"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A25" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="17">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="18"/>
+      <c r="AH25" s="18"/>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="18"/>
+      <c r="AL25" s="18"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="18"/>
+      <c r="AP25" s="18"/>
+      <c r="AQ25" s="18"/>
+      <c r="AR25" s="18"/>
+    </row>
+    <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A26" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="20">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="18"/>
+      <c r="AP26" s="18"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="18"/>
+    </row>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="17">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="18"/>
+      <c r="AA27" s="18"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="18"/>
+      <c r="AE27" s="18"/>
+      <c r="AF27" s="18"/>
+      <c r="AG27" s="18"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="18"/>
+      <c r="AL27" s="18"/>
+      <c r="AM27" s="19"/>
+      <c r="AN27" s="19"/>
+      <c r="AO27" s="18"/>
+      <c r="AP27" s="18"/>
+      <c r="AQ27" s="18"/>
+      <c r="AR27" s="18"/>
+    </row>
+    <row r="28" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A28" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="18"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="18"/>
+      <c r="AG28" s="18"/>
+      <c r="AH28" s="18"/>
+      <c r="AI28" s="18"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="18"/>
+      <c r="AL28" s="18"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="18"/>
+      <c r="AP28" s="18"/>
+      <c r="AQ28" s="18"/>
+      <c r="AR28" s="18"/>
+    </row>
+    <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A29" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="20">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="18"/>
+      <c r="AF29" s="18"/>
+      <c r="AG29" s="18"/>
+      <c r="AH29" s="18"/>
+      <c r="AI29" s="18"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="18"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="18"/>
+      <c r="AP29" s="18"/>
+      <c r="AQ29" s="18"/>
+      <c r="AR29" s="18"/>
+    </row>
+    <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A30" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="18"/>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="18"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="18"/>
+      <c r="AE30" s="18"/>
+      <c r="AF30" s="18"/>
+      <c r="AG30" s="18"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="18"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18"/>
+      <c r="AL30" s="18"/>
+      <c r="AM30" s="19"/>
+      <c r="AN30" s="19"/>
+      <c r="AO30" s="18"/>
+      <c r="AP30" s="18"/>
+      <c r="AQ30" s="18"/>
+      <c r="AR30" s="18"/>
+    </row>
+    <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="20">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="18"/>
+      <c r="AD31" s="18"/>
+      <c r="AE31" s="18"/>
+      <c r="AF31" s="18"/>
+      <c r="AG31" s="18"/>
+      <c r="AH31" s="18"/>
+      <c r="AI31" s="18"/>
+      <c r="AJ31" s="18"/>
+      <c r="AK31" s="18"/>
+      <c r="AL31" s="18"/>
+      <c r="AM31" s="19"/>
+      <c r="AN31" s="19"/>
+      <c r="AO31" s="18"/>
+      <c r="AP31" s="18"/>
+      <c r="AQ31" s="18"/>
+      <c r="AR31" s="18"/>
+    </row>
+    <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A32" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
+      <c r="Z32" s="18"/>
+      <c r="AA32" s="18"/>
+      <c r="AB32" s="18"/>
+      <c r="AC32" s="18"/>
+      <c r="AD32" s="18"/>
+      <c r="AE32" s="18"/>
+      <c r="AF32" s="18"/>
+      <c r="AG32" s="18"/>
+      <c r="AH32" s="18"/>
+      <c r="AI32" s="18"/>
+      <c r="AJ32" s="18"/>
+      <c r="AK32" s="18"/>
+      <c r="AL32" s="18"/>
+      <c r="AM32" s="19"/>
+      <c r="AN32" s="19"/>
+      <c r="AO32" s="18"/>
+      <c r="AP32" s="18"/>
+      <c r="AQ32" s="18"/>
+      <c r="AR32" s="18"/>
+    </row>
+    <row r="33" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A33" s="8"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="18"/>
+      <c r="Z33" s="18"/>
+      <c r="AA33" s="18"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="18"/>
+      <c r="AE33" s="18"/>
+      <c r="AF33" s="18"/>
+      <c r="AG33" s="18"/>
+      <c r="AH33" s="18"/>
+      <c r="AI33" s="18"/>
+      <c r="AJ33" s="18"/>
+      <c r="AK33" s="18"/>
+      <c r="AL33" s="18"/>
+      <c r="AM33" s="19"/>
+      <c r="AN33" s="19"/>
+      <c r="AO33" s="18"/>
+      <c r="AP33" s="18"/>
+      <c r="AQ33" s="18"/>
+      <c r="AR33" s="18"/>
+    </row>
+    <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="23">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="23">
+        <v>2022</v>
+      </c>
+      <c r="F34" s="23">
+        <v>2023</v>
+      </c>
+      <c r="G34" s="23">
+        <v>2024</v>
+      </c>
+      <c r="H34" s="23">
+        <v>2025</v>
+      </c>
+      <c r="I34" s="23">
+        <v>2026</v>
+      </c>
+      <c r="J34" s="23">
+        <v>2027</v>
+      </c>
+      <c r="K34" s="23">
+        <v>2028</v>
+      </c>
+      <c r="L34" s="23">
+        <v>2029</v>
+      </c>
+      <c r="M34" s="23">
+        <v>2030</v>
+      </c>
+      <c r="N34" s="23">
+        <v>2031</v>
+      </c>
+      <c r="O34" s="23">
+        <v>2032</v>
+      </c>
+      <c r="P34" s="23">
+        <v>2033</v>
+      </c>
+      <c r="Q34" s="23">
+        <v>2034</v>
+      </c>
+      <c r="R34" s="23">
+        <v>2035</v>
+      </c>
+      <c r="S34" s="23">
+        <v>2036</v>
+      </c>
+      <c r="T34" s="23">
+        <v>2037</v>
+      </c>
+      <c r="U34" s="23">
+        <v>2038</v>
+      </c>
+      <c r="V34" s="23">
+        <v>2039</v>
+      </c>
+      <c r="W34" s="23">
+        <v>2040</v>
+      </c>
+      <c r="X34" s="23">
+        <v>2041</v>
+      </c>
+      <c r="Y34" s="23">
+        <v>2042</v>
+      </c>
+      <c r="Z34" s="23">
+        <v>2043</v>
+      </c>
+      <c r="AA34" s="23">
+        <v>2044</v>
+      </c>
+      <c r="AB34" s="23">
+        <v>2045</v>
+      </c>
+      <c r="AC34" s="23">
+        <v>2046</v>
+      </c>
+      <c r="AD34" s="23">
+        <v>2047</v>
+      </c>
+      <c r="AE34" s="23">
+        <v>2048</v>
+      </c>
+      <c r="AF34" s="23">
+        <v>2049</v>
+      </c>
+      <c r="AG34" s="23">
+        <v>2050</v>
+      </c>
+      <c r="AH34" s="23">
+        <v>2051</v>
+      </c>
+      <c r="AI34" s="23">
+        <v>2052</v>
+      </c>
+      <c r="AJ34" s="23">
+        <v>2053</v>
+      </c>
+      <c r="AK34" s="23">
+        <v>2054</v>
+      </c>
+      <c r="AL34" s="23">
+        <v>2055</v>
+      </c>
+      <c r="AM34" s="23">
+        <v>2056</v>
+      </c>
+      <c r="AN34" s="23">
+        <v>2057</v>
+      </c>
+      <c r="AO34" s="23">
+        <v>2058</v>
+      </c>
+      <c r="AP34" s="23">
+        <v>2059</v>
+      </c>
+      <c r="AQ34" s="23">
+        <v>2060</v>
+      </c>
+      <c r="AR34" s="18"/>
+    </row>
+    <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A35" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="R37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="S37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="T37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="V37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="W37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="X37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AM37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AP37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ37" s="10" t="s">
-        <v>18</v>
+      <c r="B35" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="U35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="V35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="W35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="X35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR35" s="18"/>
+    </row>
+    <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A36" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="20">
+        <v>0</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0</v>
+      </c>
+      <c r="F36" s="20">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <v>0</v>
+      </c>
+      <c r="H36" s="20">
+        <v>0</v>
+      </c>
+      <c r="I36" s="20">
+        <v>0</v>
+      </c>
+      <c r="J36" s="20">
+        <v>0</v>
+      </c>
+      <c r="K36" s="20">
+        <v>0</v>
+      </c>
+      <c r="L36" s="20">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20">
+        <v>0</v>
+      </c>
+      <c r="P36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="20">
+        <v>0</v>
+      </c>
+      <c r="R36" s="20">
+        <v>0</v>
+      </c>
+      <c r="S36" s="20">
+        <v>0</v>
+      </c>
+      <c r="T36" s="20">
+        <v>0</v>
+      </c>
+      <c r="U36" s="20">
+        <v>0</v>
+      </c>
+      <c r="V36" s="20">
+        <v>0</v>
+      </c>
+      <c r="W36" s="20">
+        <v>0</v>
+      </c>
+      <c r="X36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="18"/>
+    </row>
+    <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>0</v>
+      </c>
+      <c r="P37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="20">
+        <v>0</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
+        <v>0</v>
+      </c>
+      <c r="T37" s="20">
+        <v>0</v>
+      </c>
+      <c r="U37" s="20">
+        <v>0</v>
+      </c>
+      <c r="V37" s="20">
+        <v>0</v>
+      </c>
+      <c r="W37" s="20">
+        <v>0</v>
+      </c>
+      <c r="X37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="20">
+        <v>0</v>
       </c>
       <c r="AR37" s="18"/>
     </row>
     <row r="38" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A38" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="20">
-        <v>0</v>
-      </c>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="20">
-        <v>0</v>
-      </c>
-      <c r="K38" s="20">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>0</v>
-      </c>
-      <c r="N38" s="20">
-        <v>0</v>
-      </c>
-      <c r="O38" s="20">
-        <v>0</v>
-      </c>
-      <c r="P38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="20">
-        <v>0</v>
-      </c>
-      <c r="R38" s="20">
-        <v>0</v>
-      </c>
-      <c r="S38" s="20">
-        <v>0</v>
-      </c>
-      <c r="T38" s="20">
-        <v>0</v>
-      </c>
-      <c r="U38" s="20">
-        <v>0</v>
-      </c>
-      <c r="V38" s="20">
-        <v>0</v>
-      </c>
-      <c r="W38" s="20">
-        <v>0</v>
-      </c>
-      <c r="X38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="20">
-        <v>0</v>
-      </c>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+      <c r="AG38" s="18"/>
+      <c r="AH38" s="18"/>
+      <c r="AI38" s="18"/>
+      <c r="AJ38" s="19"/>
+      <c r="AK38" s="19"/>
+      <c r="AL38" s="18"/>
+      <c r="AM38" s="19"/>
+      <c r="AN38" s="19"/>
+      <c r="AO38" s="18"/>
+      <c r="AP38" s="18"/>
+      <c r="AQ38" s="18"/>
       <c r="AR38" s="18"/>
     </row>
     <row r="39" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A39" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="20">
-        <v>0</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20">
-        <v>0</v>
-      </c>
-      <c r="H39" s="20">
-        <v>0</v>
-      </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>0</v>
-      </c>
-      <c r="K39" s="20">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20">
-        <v>0</v>
-      </c>
-      <c r="N39" s="20">
-        <v>0</v>
-      </c>
-      <c r="O39" s="20">
-        <v>0</v>
-      </c>
-      <c r="P39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0</v>
-      </c>
-      <c r="T39" s="20">
-        <v>0</v>
-      </c>
-      <c r="U39" s="20">
-        <v>0</v>
-      </c>
-      <c r="V39" s="20">
-        <v>0</v>
-      </c>
-      <c r="W39" s="20">
-        <v>0</v>
-      </c>
-      <c r="X39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="20">
-        <v>0</v>
-      </c>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="18"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
+      <c r="AF39" s="18"/>
+      <c r="AG39" s="18"/>
+      <c r="AH39" s="18"/>
+      <c r="AI39" s="18"/>
+      <c r="AJ39" s="19"/>
+      <c r="AK39" s="19"/>
+      <c r="AL39" s="18"/>
+      <c r="AM39" s="19"/>
+      <c r="AN39" s="19"/>
+      <c r="AO39" s="18"/>
+      <c r="AP39" s="18"/>
+      <c r="AQ39" s="18"/>
       <c r="AR39" s="18"/>
     </row>
     <row r="40" spans="1:44" ht="16" x14ac:dyDescent="0.4">
@@ -3791,86 +5904,28 @@
       <c r="AQ42" s="18"/>
       <c r="AR42" s="18"/>
     </row>
-    <row r="43" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="18"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="18"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="19"/>
-      <c r="AK43" s="19"/>
-      <c r="AL43" s="18"/>
-      <c r="AM43" s="18"/>
-      <c r="AN43" s="18"/>
-      <c r="AO43" s="18"/>
-      <c r="AP43" s="18"/>
-      <c r="AQ43" s="18"/>
-      <c r="AR43" s="18"/>
-    </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="AJ44" s="3"/>
-      <c r="AK44" s="3"/>
-    </row>
-    <row r="45" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="AJ45" s="3"/>
-      <c r="AK45" s="3"/>
-    </row>
-    <row r="46" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="AJ46" s="3"/>
-      <c r="AK46" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D14:AJ14 A37:AQ37">
-    <cfRule type="cellIs" dxfId="53" priority="19" operator="equal">
+  <conditionalFormatting sqref="A35:AQ35">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:C14">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:C30">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="B13:AJ13">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3878,14 +5933,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
-  <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR42"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1923DA0E-602E-4263-A988-9246800451B4}">
+  <sheetPr codeName="Hoja3"/>
+  <dimension ref="A1:AR28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.6328125" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" customWidth="1"/>
+    <col min="1" max="1" width="39.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
@@ -3942,7 +5997,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>7</v>
@@ -4040,2493 +6095,6 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="18"/>
-      <c r="AK4" s="18"/>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="19"/>
-      <c r="AO4" s="18"/>
-      <c r="AP4" s="18"/>
-      <c r="AQ4" s="18"/>
-      <c r="AR4" s="18"/>
-    </row>
-    <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AE5" s="18"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="18"/>
-      <c r="AH5" s="18"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="18"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="19"/>
-      <c r="AN5" s="19"/>
-      <c r="AO5" s="18"/>
-      <c r="AP5" s="18"/>
-      <c r="AQ5" s="18"/>
-      <c r="AR5" s="18"/>
-    </row>
-    <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="20">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="18"/>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="18"/>
-      <c r="AI6" s="18"/>
-      <c r="AJ6" s="18"/>
-      <c r="AK6" s="18"/>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="19"/>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="18"/>
-      <c r="AP6" s="18"/>
-      <c r="AQ6" s="18"/>
-      <c r="AR6" s="18"/>
-    </row>
-    <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="20">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="18"/>
-      <c r="AB7" s="18"/>
-      <c r="AC7" s="18"/>
-      <c r="AD7" s="18"/>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="18"/>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="18"/>
-      <c r="AI7" s="18"/>
-      <c r="AJ7" s="18"/>
-      <c r="AK7" s="18"/>
-      <c r="AL7" s="18"/>
-      <c r="AM7" s="19"/>
-      <c r="AN7" s="19"/>
-      <c r="AO7" s="18"/>
-      <c r="AP7" s="18"/>
-      <c r="AQ7" s="18"/>
-      <c r="AR7" s="18"/>
-    </row>
-    <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="20">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="18"/>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="18"/>
-      <c r="AE8" s="18"/>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="18"/>
-      <c r="AH8" s="18"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="18"/>
-      <c r="AK8" s="18"/>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="18"/>
-      <c r="AQ8" s="18"/>
-      <c r="AR8" s="18"/>
-    </row>
-    <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="18"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="18"/>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="18"/>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="18"/>
-    </row>
-    <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="18"/>
-      <c r="AE10" s="18"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="18"/>
-      <c r="AH10" s="18"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="18"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="18"/>
-      <c r="AP10" s="18"/>
-      <c r="AQ10" s="18"/>
-      <c r="AR10" s="18"/>
-    </row>
-    <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="17">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="18"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="18"/>
-      <c r="Y11" s="18"/>
-      <c r="Z11" s="18"/>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="18"/>
-      <c r="AC11" s="18"/>
-      <c r="AD11" s="18"/>
-      <c r="AE11" s="18"/>
-      <c r="AF11" s="18"/>
-      <c r="AG11" s="18"/>
-      <c r="AH11" s="18"/>
-      <c r="AI11" s="18"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="18"/>
-      <c r="AM11" s="18"/>
-      <c r="AN11" s="18"/>
-      <c r="AO11" s="18"/>
-      <c r="AP11" s="18"/>
-      <c r="AQ11" s="18"/>
-      <c r="AR11" s="18"/>
-    </row>
-    <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="18"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="18"/>
-      <c r="Y12" s="18"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="18"/>
-      <c r="AD12" s="18"/>
-      <c r="AE12" s="18"/>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="18"/>
-      <c r="AH12" s="18"/>
-      <c r="AI12" s="18"/>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="18"/>
-      <c r="AM12" s="18"/>
-      <c r="AN12" s="18"/>
-      <c r="AO12" s="18"/>
-      <c r="AP12" s="18"/>
-      <c r="AQ12" s="18"/>
-      <c r="AR12" s="18"/>
-    </row>
-    <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="17">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="18"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="18"/>
-      <c r="Y13" s="18"/>
-      <c r="Z13" s="18"/>
-      <c r="AA13" s="18"/>
-      <c r="AB13" s="18"/>
-      <c r="AC13" s="18"/>
-      <c r="AD13" s="18"/>
-      <c r="AE13" s="18"/>
-      <c r="AF13" s="18"/>
-      <c r="AG13" s="18"/>
-      <c r="AH13" s="18"/>
-      <c r="AI13" s="18"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="18"/>
-      <c r="AM13" s="18"/>
-      <c r="AN13" s="18"/>
-      <c r="AO13" s="18"/>
-      <c r="AP13" s="18"/>
-      <c r="AQ13" s="18"/>
-      <c r="AR13" s="18"/>
-    </row>
-    <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="18"/>
-      <c r="AE14" s="18"/>
-      <c r="AF14" s="18"/>
-      <c r="AG14" s="18"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="18"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="18"/>
-      <c r="AR14" s="18"/>
-    </row>
-    <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="20">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="18"/>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="18"/>
-      <c r="AC15" s="18"/>
-      <c r="AD15" s="18"/>
-      <c r="AE15" s="18"/>
-      <c r="AF15" s="18"/>
-      <c r="AG15" s="18"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="18"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="19"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="18"/>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="18"/>
-      <c r="AR15" s="18"/>
-    </row>
-    <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="20">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="18"/>
-      <c r="Z16" s="18"/>
-      <c r="AA16" s="18"/>
-      <c r="AB16" s="18"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="18"/>
-      <c r="AE16" s="18"/>
-      <c r="AF16" s="18"/>
-      <c r="AG16" s="18"/>
-      <c r="AH16" s="18"/>
-      <c r="AI16" s="18"/>
-      <c r="AJ16" s="18"/>
-      <c r="AK16" s="18"/>
-      <c r="AL16" s="18"/>
-      <c r="AM16" s="19"/>
-      <c r="AN16" s="19"/>
-      <c r="AO16" s="18"/>
-      <c r="AP16" s="18"/>
-      <c r="AQ16" s="18"/>
-      <c r="AR16" s="18"/>
-    </row>
-    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A17" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="20">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="18"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="18"/>
-      <c r="AD17" s="18"/>
-      <c r="AE17" s="18"/>
-      <c r="AF17" s="18"/>
-      <c r="AG17" s="18"/>
-      <c r="AH17" s="18"/>
-      <c r="AI17" s="18"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="18"/>
-      <c r="AL17" s="18"/>
-      <c r="AM17" s="19"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="18"/>
-      <c r="AP17" s="18"/>
-      <c r="AQ17" s="18"/>
-      <c r="AR17" s="18"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="18"/>
-      <c r="AC18" s="18"/>
-      <c r="AD18" s="18"/>
-      <c r="AE18" s="18"/>
-      <c r="AF18" s="18"/>
-      <c r="AG18" s="18"/>
-      <c r="AH18" s="18"/>
-      <c r="AI18" s="18"/>
-      <c r="AJ18" s="18"/>
-      <c r="AK18" s="18"/>
-      <c r="AL18" s="18"/>
-      <c r="AM18" s="19"/>
-      <c r="AN18" s="19"/>
-      <c r="AO18" s="18"/>
-      <c r="AP18" s="18"/>
-      <c r="AQ18" s="18"/>
-      <c r="AR18" s="18"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="18"/>
-      <c r="AD19" s="18"/>
-      <c r="AE19" s="18"/>
-      <c r="AF19" s="18"/>
-      <c r="AG19" s="18"/>
-      <c r="AH19" s="18"/>
-      <c r="AI19" s="18"/>
-      <c r="AJ19" s="18"/>
-      <c r="AK19" s="18"/>
-      <c r="AL19" s="18"/>
-      <c r="AM19" s="19"/>
-      <c r="AN19" s="19"/>
-      <c r="AO19" s="18"/>
-      <c r="AP19" s="18"/>
-      <c r="AQ19" s="18"/>
-      <c r="AR19" s="18"/>
-    </row>
-    <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="18"/>
-      <c r="AC20" s="18"/>
-      <c r="AD20" s="18"/>
-      <c r="AE20" s="18"/>
-      <c r="AF20" s="18"/>
-      <c r="AG20" s="18"/>
-      <c r="AH20" s="18"/>
-      <c r="AI20" s="18"/>
-      <c r="AJ20" s="18"/>
-      <c r="AK20" s="18"/>
-      <c r="AL20" s="18"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="18"/>
-      <c r="AP20" s="18"/>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="18"/>
-    </row>
-    <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-      <c r="AE21" s="18"/>
-      <c r="AF21" s="18"/>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="18"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="19"/>
-      <c r="AN21" s="19"/>
-      <c r="AO21" s="18"/>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="18"/>
-      <c r="AR21" s="18"/>
-    </row>
-    <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="20">
-        <v>0</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="18"/>
-      <c r="AD22" s="18"/>
-      <c r="AE22" s="18"/>
-      <c r="AF22" s="18"/>
-      <c r="AG22" s="18"/>
-      <c r="AH22" s="18"/>
-      <c r="AI22" s="18"/>
-      <c r="AJ22" s="18"/>
-      <c r="AK22" s="18"/>
-      <c r="AL22" s="18"/>
-      <c r="AM22" s="19"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="18"/>
-      <c r="AP22" s="18"/>
-      <c r="AQ22" s="18"/>
-      <c r="AR22" s="18"/>
-    </row>
-    <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="20">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="18"/>
-      <c r="AE23" s="18"/>
-      <c r="AF23" s="18"/>
-      <c r="AG23" s="18"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="18"/>
-      <c r="AJ23" s="18"/>
-      <c r="AK23" s="18"/>
-      <c r="AL23" s="18"/>
-      <c r="AM23" s="19"/>
-      <c r="AN23" s="19"/>
-      <c r="AO23" s="18"/>
-      <c r="AP23" s="18"/>
-      <c r="AQ23" s="18"/>
-      <c r="AR23" s="18"/>
-    </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="20">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="18"/>
-      <c r="AE24" s="18"/>
-      <c r="AF24" s="18"/>
-      <c r="AG24" s="18"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
-      <c r="AK24" s="18"/>
-      <c r="AL24" s="18"/>
-      <c r="AM24" s="19"/>
-      <c r="AN24" s="19"/>
-      <c r="AO24" s="18"/>
-      <c r="AP24" s="18"/>
-      <c r="AQ24" s="18"/>
-      <c r="AR24" s="18"/>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="18"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="18"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="19"/>
-      <c r="AN25" s="19"/>
-      <c r="AO25" s="18"/>
-      <c r="AP25" s="18"/>
-      <c r="AQ25" s="18"/>
-      <c r="AR25" s="18"/>
-    </row>
-    <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="19"/>
-      <c r="AN26" s="19"/>
-      <c r="AO26" s="18"/>
-      <c r="AP26" s="18"/>
-      <c r="AQ26" s="18"/>
-      <c r="AR26" s="18"/>
-    </row>
-    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A27" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="17">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="19"/>
-      <c r="AN27" s="19"/>
-      <c r="AO27" s="18"/>
-      <c r="AP27" s="18"/>
-      <c r="AQ27" s="18"/>
-      <c r="AR27" s="18"/>
-    </row>
-    <row r="28" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A28" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20">
-        <v>0</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="18"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="18"/>
-      <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="19"/>
-      <c r="AN28" s="19"/>
-      <c r="AO28" s="18"/>
-      <c r="AP28" s="18"/>
-      <c r="AQ28" s="18"/>
-      <c r="AR28" s="18"/>
-    </row>
-    <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A29" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="17">
-        <v>0</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="18"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="19"/>
-      <c r="AN29" s="19"/>
-      <c r="AO29" s="18"/>
-      <c r="AP29" s="18"/>
-      <c r="AQ29" s="18"/>
-      <c r="AR29" s="18"/>
-    </row>
-    <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A30" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="18"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="19"/>
-      <c r="AN30" s="19"/>
-      <c r="AO30" s="18"/>
-      <c r="AP30" s="18"/>
-      <c r="AQ30" s="18"/>
-      <c r="AR30" s="18"/>
-    </row>
-    <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A31" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="20">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="18"/>
-      <c r="AD31" s="18"/>
-      <c r="AE31" s="18"/>
-      <c r="AF31" s="18"/>
-      <c r="AG31" s="18"/>
-      <c r="AH31" s="18"/>
-      <c r="AI31" s="18"/>
-      <c r="AJ31" s="18"/>
-      <c r="AK31" s="18"/>
-      <c r="AL31" s="18"/>
-      <c r="AM31" s="19"/>
-      <c r="AN31" s="19"/>
-      <c r="AO31" s="18"/>
-      <c r="AP31" s="18"/>
-      <c r="AQ31" s="18"/>
-      <c r="AR31" s="18"/>
-    </row>
-    <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A32" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="20">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="18"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="18"/>
-      <c r="AF32" s="18"/>
-      <c r="AG32" s="18"/>
-      <c r="AH32" s="18"/>
-      <c r="AI32" s="18"/>
-      <c r="AJ32" s="18"/>
-      <c r="AK32" s="18"/>
-      <c r="AL32" s="18"/>
-      <c r="AM32" s="19"/>
-      <c r="AN32" s="19"/>
-      <c r="AO32" s="18"/>
-      <c r="AP32" s="18"/>
-      <c r="AQ32" s="18"/>
-      <c r="AR32" s="18"/>
-    </row>
-    <row r="33" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="20">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="18"/>
-      <c r="AE33" s="18"/>
-      <c r="AF33" s="18"/>
-      <c r="AG33" s="18"/>
-      <c r="AH33" s="18"/>
-      <c r="AI33" s="18"/>
-      <c r="AJ33" s="18"/>
-      <c r="AK33" s="18"/>
-      <c r="AL33" s="18"/>
-      <c r="AM33" s="19"/>
-      <c r="AN33" s="19"/>
-      <c r="AO33" s="18"/>
-      <c r="AP33" s="18"/>
-      <c r="AQ33" s="18"/>
-      <c r="AR33" s="18"/>
-    </row>
-    <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="17">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="18"/>
-      <c r="AD34" s="18"/>
-      <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
-      <c r="AG34" s="18"/>
-      <c r="AH34" s="18"/>
-      <c r="AI34" s="18"/>
-      <c r="AJ34" s="18"/>
-      <c r="AK34" s="18"/>
-      <c r="AL34" s="18"/>
-      <c r="AM34" s="19"/>
-      <c r="AN34" s="19"/>
-      <c r="AO34" s="18"/>
-      <c r="AP34" s="18"/>
-      <c r="AQ34" s="18"/>
-      <c r="AR34" s="18"/>
-    </row>
-    <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A35" s="8"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="18"/>
-      <c r="AE35" s="18"/>
-      <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="18"/>
-      <c r="AI35" s="18"/>
-      <c r="AJ35" s="18"/>
-      <c r="AK35" s="18"/>
-      <c r="AL35" s="18"/>
-      <c r="AM35" s="19"/>
-      <c r="AN35" s="19"/>
-      <c r="AO35" s="18"/>
-      <c r="AP35" s="18"/>
-      <c r="AQ35" s="18"/>
-      <c r="AR35" s="18"/>
-    </row>
-    <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="23">
-        <v>2021</v>
-      </c>
-      <c r="E36" s="23">
-        <v>2022</v>
-      </c>
-      <c r="F36" s="23">
-        <v>2023</v>
-      </c>
-      <c r="G36" s="23">
-        <v>2024</v>
-      </c>
-      <c r="H36" s="23">
-        <v>2025</v>
-      </c>
-      <c r="I36" s="23">
-        <v>2026</v>
-      </c>
-      <c r="J36" s="23">
-        <v>2027</v>
-      </c>
-      <c r="K36" s="23">
-        <v>2028</v>
-      </c>
-      <c r="L36" s="23">
-        <v>2029</v>
-      </c>
-      <c r="M36" s="23">
-        <v>2030</v>
-      </c>
-      <c r="N36" s="23">
-        <v>2031</v>
-      </c>
-      <c r="O36" s="23">
-        <v>2032</v>
-      </c>
-      <c r="P36" s="23">
-        <v>2033</v>
-      </c>
-      <c r="Q36" s="23">
-        <v>2034</v>
-      </c>
-      <c r="R36" s="23">
-        <v>2035</v>
-      </c>
-      <c r="S36" s="23">
-        <v>2036</v>
-      </c>
-      <c r="T36" s="23">
-        <v>2037</v>
-      </c>
-      <c r="U36" s="23">
-        <v>2038</v>
-      </c>
-      <c r="V36" s="23">
-        <v>2039</v>
-      </c>
-      <c r="W36" s="23">
-        <v>2040</v>
-      </c>
-      <c r="X36" s="23">
-        <v>2041</v>
-      </c>
-      <c r="Y36" s="23">
-        <v>2042</v>
-      </c>
-      <c r="Z36" s="23">
-        <v>2043</v>
-      </c>
-      <c r="AA36" s="23">
-        <v>2044</v>
-      </c>
-      <c r="AB36" s="23">
-        <v>2045</v>
-      </c>
-      <c r="AC36" s="23">
-        <v>2046</v>
-      </c>
-      <c r="AD36" s="23">
-        <v>2047</v>
-      </c>
-      <c r="AE36" s="23">
-        <v>2048</v>
-      </c>
-      <c r="AF36" s="23">
-        <v>2049</v>
-      </c>
-      <c r="AG36" s="23">
-        <v>2050</v>
-      </c>
-      <c r="AH36" s="23">
-        <v>2051</v>
-      </c>
-      <c r="AI36" s="23">
-        <v>2052</v>
-      </c>
-      <c r="AJ36" s="23">
-        <v>2053</v>
-      </c>
-      <c r="AK36" s="23">
-        <v>2054</v>
-      </c>
-      <c r="AL36" s="23">
-        <v>2055</v>
-      </c>
-      <c r="AM36" s="23">
-        <v>2056</v>
-      </c>
-      <c r="AN36" s="23">
-        <v>2057</v>
-      </c>
-      <c r="AO36" s="23">
-        <v>2058</v>
-      </c>
-      <c r="AP36" s="23">
-        <v>2059</v>
-      </c>
-      <c r="AQ36" s="23">
-        <v>2060</v>
-      </c>
-      <c r="AR36" s="18"/>
-    </row>
-    <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A37" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="R37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="S37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="T37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="V37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="W37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="X37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AM37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AP37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AR37" s="18"/>
-    </row>
-    <row r="38" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A38" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="20">
-        <v>0</v>
-      </c>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="20">
-        <v>0</v>
-      </c>
-      <c r="K38" s="20">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>0</v>
-      </c>
-      <c r="N38" s="20">
-        <v>0</v>
-      </c>
-      <c r="O38" s="20">
-        <v>0</v>
-      </c>
-      <c r="P38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="20">
-        <v>0</v>
-      </c>
-      <c r="R38" s="20">
-        <v>0</v>
-      </c>
-      <c r="S38" s="20">
-        <v>0</v>
-      </c>
-      <c r="T38" s="20">
-        <v>0</v>
-      </c>
-      <c r="U38" s="20">
-        <v>0</v>
-      </c>
-      <c r="V38" s="20">
-        <v>0</v>
-      </c>
-      <c r="W38" s="20">
-        <v>0</v>
-      </c>
-      <c r="X38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="18"/>
-    </row>
-    <row r="39" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A39" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="20">
-        <v>0</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20">
-        <v>0</v>
-      </c>
-      <c r="H39" s="20">
-        <v>0</v>
-      </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>0</v>
-      </c>
-      <c r="K39" s="20">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20">
-        <v>0</v>
-      </c>
-      <c r="N39" s="20">
-        <v>0</v>
-      </c>
-      <c r="O39" s="20">
-        <v>0</v>
-      </c>
-      <c r="P39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>0</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0</v>
-      </c>
-      <c r="T39" s="20">
-        <v>0</v>
-      </c>
-      <c r="U39" s="20">
-        <v>0</v>
-      </c>
-      <c r="V39" s="20">
-        <v>0</v>
-      </c>
-      <c r="W39" s="20">
-        <v>0</v>
-      </c>
-      <c r="X39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="20">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="18"/>
-    </row>
-    <row r="40" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18"/>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="18"/>
-      <c r="AD40" s="18"/>
-      <c r="AE40" s="18"/>
-      <c r="AF40" s="18"/>
-      <c r="AG40" s="18"/>
-      <c r="AH40" s="18"/>
-      <c r="AI40" s="18"/>
-      <c r="AJ40" s="19"/>
-      <c r="AK40" s="19"/>
-      <c r="AL40" s="18"/>
-      <c r="AM40" s="19"/>
-      <c r="AN40" s="19"/>
-      <c r="AO40" s="18"/>
-      <c r="AP40" s="18"/>
-      <c r="AQ40" s="18"/>
-      <c r="AR40" s="18"/>
-    </row>
-    <row r="41" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18"/>
-      <c r="AB41" s="18"/>
-      <c r="AC41" s="18"/>
-      <c r="AD41" s="18"/>
-      <c r="AE41" s="18"/>
-      <c r="AF41" s="18"/>
-      <c r="AG41" s="18"/>
-      <c r="AH41" s="18"/>
-      <c r="AI41" s="18"/>
-      <c r="AJ41" s="19"/>
-      <c r="AK41" s="19"/>
-      <c r="AL41" s="18"/>
-      <c r="AM41" s="19"/>
-      <c r="AN41" s="19"/>
-      <c r="AO41" s="18"/>
-      <c r="AP41" s="18"/>
-      <c r="AQ41" s="18"/>
-      <c r="AR41" s="18"/>
-    </row>
-    <row r="42" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
-      <c r="AB42" s="18"/>
-      <c r="AC42" s="18"/>
-      <c r="AD42" s="18"/>
-      <c r="AE42" s="18"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="18"/>
-      <c r="AI42" s="18"/>
-      <c r="AJ42" s="19"/>
-      <c r="AK42" s="19"/>
-      <c r="AL42" s="18"/>
-      <c r="AM42" s="18"/>
-      <c r="AN42" s="18"/>
-      <c r="AO42" s="18"/>
-      <c r="AP42" s="18"/>
-      <c r="AQ42" s="18"/>
-      <c r="AR42" s="18"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D14:AJ14 A37:AQ37">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:C14">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:C30">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1923DA0E-602E-4263-A988-9246800451B4}">
-  <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AR28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="39.36328125" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15"/>
-    </row>
-    <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="17">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="18"/>
-      <c r="AP2" s="18"/>
-      <c r="AQ2" s="18"/>
-      <c r="AR2" s="18"/>
-    </row>
-    <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="18"/>
-      <c r="AC3" s="18"/>
-      <c r="AD3" s="18"/>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="18"/>
-      <c r="AG3" s="18"/>
-      <c r="AH3" s="18"/>
-      <c r="AI3" s="18"/>
-      <c r="AJ3" s="18"/>
-      <c r="AK3" s="18"/>
-      <c r="AL3" s="18"/>
-      <c r="AM3" s="19"/>
-      <c r="AN3" s="19"/>
-      <c r="AO3" s="18"/>
-      <c r="AP3" s="18"/>
-      <c r="AQ3" s="18"/>
-      <c r="AR3" s="18"/>
-    </row>
-    <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -6833,7 +6401,7 @@
     </row>
     <row r="10" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>0</v>
@@ -6885,7 +6453,7 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>0</v>
@@ -6937,7 +6505,7 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>0</v>
@@ -6989,7 +6557,7 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>18</v>
@@ -7041,7 +6609,7 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>0</v>
@@ -7197,7 +6765,7 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>0</v>
@@ -7248,9 +6816,9 @@
       <c r="AR17" s="18"/>
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -8015,26 +7583,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:AJ11">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:AJ14 A20:AQ20">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:AJ11">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/LPG testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1206A59A-34C6-48C2-B0D0-D26759766E4D}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EFB680D-0997-4CE1-A38F-AB0E77F3A992}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="52">
   <si>
     <t>%</t>
   </si>
@@ -335,7 +335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,12 +402,75 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2097,128 +2160,128 @@
       <c r="B22" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="18">
-        <v>0</v>
-      </c>
-      <c r="D22" s="18">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="18">
-        <v>0</v>
-      </c>
-      <c r="G22" s="18">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="18">
-        <v>0</v>
-      </c>
-      <c r="K22" s="18">
-        <v>0</v>
-      </c>
-      <c r="L22" s="18">
-        <v>0</v>
-      </c>
-      <c r="M22" s="18">
-        <v>0</v>
-      </c>
-      <c r="N22" s="18">
-        <v>0</v>
-      </c>
-      <c r="O22" s="18">
-        <v>0</v>
-      </c>
-      <c r="P22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="18">
-        <v>0</v>
-      </c>
-      <c r="R22" s="18">
-        <v>0</v>
-      </c>
-      <c r="S22" s="18">
-        <v>0</v>
-      </c>
-      <c r="T22" s="18">
-        <v>0</v>
-      </c>
-      <c r="U22" s="18">
-        <v>0</v>
-      </c>
-      <c r="V22" s="18">
-        <v>0</v>
-      </c>
-      <c r="W22" s="18">
-        <v>0</v>
-      </c>
-      <c r="X22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="18">
-        <v>0</v>
+      <c r="C22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="U22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ22" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
@@ -3100,26 +3163,34 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A22:B22">
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:AQ22">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4304,128 +4375,128 @@
       <c r="B22" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="18">
-        <v>0</v>
-      </c>
-      <c r="D22" s="18">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="18">
-        <v>0</v>
-      </c>
-      <c r="G22" s="18">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="18">
-        <v>0</v>
-      </c>
-      <c r="K22" s="18">
-        <v>0</v>
-      </c>
-      <c r="L22" s="18">
-        <v>0</v>
-      </c>
-      <c r="M22" s="18">
-        <v>0</v>
-      </c>
-      <c r="N22" s="18">
-        <v>0</v>
-      </c>
-      <c r="O22" s="18">
-        <v>0</v>
-      </c>
-      <c r="P22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="18">
-        <v>0</v>
-      </c>
-      <c r="R22" s="18">
-        <v>0</v>
-      </c>
-      <c r="S22" s="18">
-        <v>0</v>
-      </c>
-      <c r="T22" s="18">
-        <v>0</v>
-      </c>
-      <c r="U22" s="18">
-        <v>0</v>
-      </c>
-      <c r="V22" s="18">
-        <v>0</v>
-      </c>
-      <c r="W22" s="18">
-        <v>0</v>
-      </c>
-      <c r="X22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="18">
-        <v>0</v>
+      <c r="C22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="U22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ22" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
@@ -5444,27 +5515,35 @@
       <c r="AR42" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22:B22">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="A22">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:AQ22">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6135,128 +6214,128 @@
       <c r="B12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="18">
-        <v>0</v>
-      </c>
-      <c r="D12" s="18">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18">
-        <v>0</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>0</v>
-      </c>
-      <c r="R12" s="18">
-        <v>0</v>
-      </c>
-      <c r="S12" s="18">
-        <v>0</v>
-      </c>
-      <c r="T12" s="18">
-        <v>0</v>
-      </c>
-      <c r="U12" s="18">
-        <v>0</v>
-      </c>
-      <c r="V12" s="18">
-        <v>0</v>
-      </c>
-      <c r="W12" s="18">
-        <v>0</v>
-      </c>
-      <c r="X12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="18">
-        <v>0</v>
+      <c r="C12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="R12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="T12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="U12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="X12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ12" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="AR12" s="16"/>
     </row>
@@ -6976,26 +7055,34 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AJ3">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:AJ6 A12:B12">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:AQ12">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/LPG testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EFB680D-0997-4CE1-A38F-AB0E77F3A992}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E91E27-747D-4DF9-8535-7A868DCDF9AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="51">
   <si>
     <t>%</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Amortization period</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Annual debt needs</t>
@@ -410,47 +407,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -995,13 +952,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -1047,7 +1004,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -1099,7 +1056,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -1151,7 +1108,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -1203,13 +1160,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1255,7 +1212,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -1307,7 +1264,7 @@
     </row>
     <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -1359,7 +1316,7 @@
     </row>
     <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -1411,7 +1368,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -1509,13 +1466,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -1561,7 +1518,7 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>0</v>
@@ -1613,7 +1570,7 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -1665,7 +1622,7 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>0</v>
@@ -1717,13 +1674,13 @@
     </row>
     <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1769,7 +1726,7 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>0</v>
@@ -1821,7 +1778,7 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -1873,7 +1830,7 @@
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -1925,7 +1882,7 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>0</v>
@@ -2023,13 +1980,13 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>4</v>
+      <c r="C21" s="21">
+        <v>2020</v>
       </c>
       <c r="D21" s="21">
         <v>2021</v>
@@ -2155,142 +2112,142 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="18">
         <v>0</v>
@@ -2419,10 +2376,10 @@
     </row>
     <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C24" s="18">
         <v>0</v>
@@ -2597,13 +2554,13 @@
     </row>
     <row r="26" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -2649,10 +2606,10 @@
     </row>
     <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="15">
         <v>0</v>
@@ -2747,13 +2704,13 @@
     </row>
     <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -2799,10 +2756,10 @@
     </row>
     <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="18">
         <v>0</v>
@@ -2851,10 +2808,10 @@
     </row>
     <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="18">
         <v>0</v>
@@ -2903,10 +2860,10 @@
     </row>
     <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="18">
         <v>0</v>
@@ -2955,13 +2912,13 @@
     </row>
     <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -3007,10 +2964,10 @@
     </row>
     <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="18">
         <v>0</v>
@@ -3059,10 +3016,10 @@
     </row>
     <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="18">
         <v>0</v>
@@ -3111,10 +3068,10 @@
     </row>
     <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18">
         <v>0</v>
@@ -3162,35 +3119,27 @@
       <c r="AR37" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22:B22">
-    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
+  <conditionalFormatting sqref="A22:AQ22">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22:AQ22">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3210,13 +3159,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -3262,7 +3211,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -3314,7 +3263,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -3366,7 +3315,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -3418,13 +3367,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -3470,7 +3419,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -3522,7 +3471,7 @@
     </row>
     <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -3574,7 +3523,7 @@
     </row>
     <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3626,7 +3575,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -3724,13 +3673,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -3776,7 +3725,7 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>0</v>
@@ -3828,7 +3777,7 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -3880,7 +3829,7 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>0</v>
@@ -3932,13 +3881,13 @@
     </row>
     <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -3984,7 +3933,7 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>0</v>
@@ -4036,7 +3985,7 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -4088,7 +4037,7 @@
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -4140,7 +4089,7 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>0</v>
@@ -4238,13 +4187,13 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>4</v>
+      <c r="C21" s="21">
+        <v>2020</v>
       </c>
       <c r="D21" s="21">
         <v>2021</v>
@@ -4370,142 +4319,142 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="18">
         <v>0</v>
@@ -4634,10 +4583,10 @@
     </row>
     <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C24" s="18">
         <v>0</v>
@@ -4812,13 +4761,13 @@
     </row>
     <row r="26" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -4864,10 +4813,10 @@
     </row>
     <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="15">
         <v>0</v>
@@ -4962,13 +4911,13 @@
     </row>
     <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -5014,10 +4963,10 @@
     </row>
     <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="18">
         <v>0</v>
@@ -5066,10 +5015,10 @@
     </row>
     <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="18">
         <v>0</v>
@@ -5118,10 +5067,10 @@
     </row>
     <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="18">
         <v>0</v>
@@ -5170,13 +5119,13 @@
     </row>
     <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -5222,10 +5171,10 @@
     </row>
     <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="18">
         <v>0</v>
@@ -5274,10 +5223,10 @@
     </row>
     <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="18">
         <v>0</v>
@@ -5326,10 +5275,10 @@
     </row>
     <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18">
         <v>0</v>
@@ -5515,35 +5464,27 @@
       <c r="AR42" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+  <conditionalFormatting sqref="A22:AQ22">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:AQ22">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5563,13 +5504,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -5615,7 +5556,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -5667,7 +5608,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -5719,7 +5660,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -5771,13 +5712,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -5823,7 +5764,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -5979,7 +5920,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -6077,13 +6018,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>4</v>
+      <c r="C11" s="21">
+        <v>2020</v>
       </c>
       <c r="D11" s="21">
         <v>2021</v>
@@ -6209,142 +6150,142 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR12" s="16"/>
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -6473,10 +6414,10 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -6651,13 +6592,13 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6703,10 +6644,10 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="15">
         <v>0</v>
@@ -6801,13 +6742,13 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -6853,10 +6794,10 @@
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -6905,10 +6846,10 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="18">
         <v>0</v>
@@ -6957,10 +6898,10 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="18">
         <v>0</v>
@@ -7054,35 +6995,35 @@
       <c r="AR23" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:C5">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="A12:AQ12">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:C5">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AJ3">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:AJ6 A12:B12">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+  <conditionalFormatting sqref="D6:AJ6">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:AQ12">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/backend/{templates}/design-capital-{model}.xlsx
+++ b/backend/{templates}/design-capital-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF04F80-47CE-41BE-8209-9827F5D06D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CAF04F80-47CE-41BE-8209-9827F5D06D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{289D7ADD-36D0-4591-A65E-9BC651F859A4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="31">
   <si>
     <t>%</t>
   </si>
@@ -129,6 +129,9 @@
   <si>
     <t xml:space="preserve">Debt </t>
   </si>
+  <si>
+    <t>Years realisation</t>
+  </si>
 </sst>
 </file>
 
@@ -215,7 +218,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,6 +240,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -358,212 +367,15 @@
     <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1080,7 +892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3833E1-9C55-460E-A922-AEA15E5E66A2}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.54296875" customWidth="1"/>
@@ -1295,15 +1107,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -1347,14 +1157,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1391,8 +1201,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -1400,10 +1210,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -1440,8 +1250,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -1452,7 +1262,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -1503,9 +1313,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1549,887 +1365,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -2473,15 +2289,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -2525,14 +2335,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2544,7 +2354,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -2578,7 +2388,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -2630,7 +2440,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -2648,7 +2458,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -2680,62 +2490,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -2776,123 +2592,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2903,7 +2677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AT26"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -3119,15 +2893,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -3171,14 +2943,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -3215,8 +2987,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -3224,10 +2996,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -3264,8 +3036,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -3276,7 +3048,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3327,9 +3099,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -3373,887 +3151,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -4297,15 +4075,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -4349,14 +4121,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -4368,7 +4140,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -4402,7 +4174,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -4454,7 +4226,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -4472,7 +4244,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -4504,62 +4276,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -4600,35 +4378,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4639,7 +4463,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1923DA0E-602E-4263-A988-9246800451B4}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" customWidth="1"/>
@@ -4855,15 +4679,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -4907,14 +4729,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -4951,8 +4773,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -4960,10 +4782,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -5000,8 +4822,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -5012,7 +4834,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -5063,9 +4885,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -5109,887 +4937,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6033,15 +5861,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -6085,14 +5907,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -6104,7 +5926,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -6138,7 +5960,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -6190,7 +6012,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -6208,7 +6030,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -6240,62 +6062,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -6336,123 +6164,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
